--- a/input_data/emission_factors.xlsx
+++ b/input_data/emission_factors.xlsx
@@ -1,30 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jan-Steffen Fischer\Desktop\REAT_to_publish\REAT_v1_external\input_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Studium\Desktop\Launch_Reentry_Data\REAT_github\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44E31BB-F486-447B-82DA-B2024480F5D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DAA843-DB15-43BB-838E-269C939507B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3225" yWindow="3315" windowWidth="10620" windowHeight="9465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Emission_Factors" sheetId="1" r:id="rId1"/>
     <sheet name="README - How to enter data" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Emission_Factors!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Emission_Factors!$A$1:$BJ$47</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="124">
   <si>
     <t>sheet: Emission_Factors</t>
   </si>
@@ -62,167 +75,348 @@
     <t>BC_prim</t>
   </si>
   <si>
+    <t>AA7475</t>
+  </si>
+  <si>
+    <t>stoichiometric</t>
+  </si>
+  <si>
+    <t>AA2219</t>
+  </si>
+  <si>
+    <t>[0,120]</t>
+  </si>
+  <si>
+    <t>Ti6Al4V</t>
+  </si>
+  <si>
+    <t>AA5056</t>
+  </si>
+  <si>
+    <t>A316</t>
+  </si>
+  <si>
+    <t>AlTi</t>
+  </si>
+  <si>
+    <t>AA2198</t>
+  </si>
+  <si>
+    <t>Al2O3</t>
+  </si>
+  <si>
+    <t>Ag2O</t>
+  </si>
+  <si>
+    <t>Cl2</t>
+  </si>
+  <si>
+    <t>Cr2O3</t>
+  </si>
+  <si>
+    <t>CuO</t>
+  </si>
+  <si>
+    <t>Fe2O3</t>
+  </si>
+  <si>
+    <t>MgO</t>
+  </si>
+  <si>
+    <t>MnO2</t>
+  </si>
+  <si>
+    <t>NiO</t>
+  </si>
+  <si>
+    <t>SiO2</t>
+  </si>
+  <si>
+    <t>SnO2</t>
+  </si>
+  <si>
+    <t>TiO2</t>
+  </si>
+  <si>
+    <t>V2O5</t>
+  </si>
+  <si>
+    <t>ZnO</t>
+  </si>
+  <si>
+    <t>CFRP</t>
+  </si>
+  <si>
+    <t>[50,55]</t>
+  </si>
+  <si>
+    <t>[55,60]</t>
+  </si>
+  <si>
+    <t>[60,65]</t>
+  </si>
+  <si>
+    <t>[65,70]</t>
+  </si>
+  <si>
+    <t>REAT</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Zn</t>
+  </si>
+  <si>
+    <t>Mg2</t>
+  </si>
+  <si>
+    <t>NO2</t>
+  </si>
+  <si>
+    <t>[45,50]</t>
+  </si>
+  <si>
+    <t>Mn</t>
+  </si>
+  <si>
+    <t>[70,75]</t>
+  </si>
+  <si>
+    <t>[35,40]</t>
+  </si>
+  <si>
+    <t>[40,45]</t>
+  </si>
+  <si>
+    <t>V4O10</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>CLO</t>
+  </si>
+  <si>
+    <t>HCl</t>
+  </si>
+  <si>
+    <t>HCN</t>
+  </si>
+  <si>
+    <t>HNC</t>
+  </si>
+  <si>
+    <t>HOCL</t>
+  </si>
+  <si>
+    <t>NH3</t>
+  </si>
+  <si>
+    <t>SiCu</t>
+  </si>
+  <si>
+    <t>AA7075</t>
+  </si>
+  <si>
+    <t>AA2195</t>
+  </si>
+  <si>
+    <t>CFRPAl</t>
+  </si>
+  <si>
+    <t>Inconel718</t>
+  </si>
+  <si>
+    <t>atomic</t>
+  </si>
+  <si>
+    <t>AL(at)</t>
+  </si>
+  <si>
+    <t>Ag(at)</t>
+  </si>
+  <si>
+    <t>C(at)</t>
+  </si>
+  <si>
+    <t>CL(at)</t>
+  </si>
+  <si>
+    <t>Cr(at)</t>
+  </si>
+  <si>
+    <t>Co(at)</t>
+  </si>
+  <si>
+    <t>Cu(at)</t>
+  </si>
+  <si>
+    <t>Fe(at)</t>
+  </si>
+  <si>
+    <t>H(at)</t>
+  </si>
+  <si>
+    <t>Li(at)</t>
+  </si>
+  <si>
+    <t>Mg(at)</t>
+  </si>
+  <si>
+    <t>Mo(at)</t>
+  </si>
+  <si>
+    <t>Mn(at)</t>
+  </si>
+  <si>
+    <t>N(at)</t>
+  </si>
+  <si>
+    <t>Nb(at)</t>
+  </si>
+  <si>
+    <t>Ni(at)</t>
+  </si>
+  <si>
+    <t>O(at)</t>
+  </si>
+  <si>
+    <t>Si(at)</t>
+  </si>
+  <si>
+    <t>Sn(at)</t>
+  </si>
+  <si>
+    <t>Ti(at)</t>
+  </si>
+  <si>
+    <t>V(at)</t>
+  </si>
+  <si>
+    <t>Zn(at)</t>
+  </si>
+  <si>
+    <t>Inconel718_Cu</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Elec</t>
+  </si>
+  <si>
+    <t>CFRP_AA7075</t>
+  </si>
+  <si>
+    <t>A316L</t>
+  </si>
+  <si>
+    <t>AA6061</t>
+  </si>
+  <si>
+    <t>AACFRP</t>
+  </si>
+  <si>
+    <t>AAITS</t>
+  </si>
+  <si>
+    <t>AATF</t>
+  </si>
+  <si>
+    <t>AATFU</t>
+  </si>
+  <si>
+    <t>AATOX</t>
+  </si>
+  <si>
+    <t>ACP</t>
+  </si>
+  <si>
+    <t>AENG</t>
+  </si>
+  <si>
+    <t>AFS</t>
+  </si>
+  <si>
+    <t>CuAgZr</t>
+  </si>
+  <si>
+    <t>Hastelloy-X</t>
+  </si>
+  <si>
+    <t>Zr(at)</t>
+  </si>
+  <si>
+    <t>Au(at)</t>
+  </si>
+  <si>
+    <t>B(at)</t>
+  </si>
+  <si>
+    <t>P(at)</t>
+  </si>
+  <si>
+    <t>Pb(at)</t>
+  </si>
+  <si>
+    <t>S(at)</t>
+  </si>
+  <si>
+    <t>Ta(at)</t>
+  </si>
+  <si>
+    <t>W(at)</t>
+  </si>
+  <si>
+    <t>Matweb</t>
+  </si>
+  <si>
+    <t>Bitondo, Prisco 2010</t>
+  </si>
+  <si>
+    <t>DIN EN 573-3</t>
+  </si>
+  <si>
+    <t>Elisental</t>
+  </si>
+  <si>
+    <t>M56 HexPly composition</t>
+  </si>
+  <si>
+    <t>VDM Alloy 718</t>
+  </si>
+  <si>
+    <t>EN ISO 5832-3</t>
+  </si>
+  <si>
     <t>notes</t>
-  </si>
-  <si>
-    <t>stoichiometric</t>
-  </si>
-  <si>
-    <t>AA2219</t>
-  </si>
-  <si>
-    <t>[0,120]</t>
-  </si>
-  <si>
-    <t>Ti6Al4V</t>
-  </si>
-  <si>
-    <t>A316</t>
-  </si>
-  <si>
-    <t>AlTi</t>
-  </si>
-  <si>
-    <t>AA2198</t>
-  </si>
-  <si>
-    <t>Al2O3</t>
-  </si>
-  <si>
-    <t>Ag2O</t>
-  </si>
-  <si>
-    <t>Cl2</t>
-  </si>
-  <si>
-    <t>Cr2O3</t>
-  </si>
-  <si>
-    <t>CuO</t>
-  </si>
-  <si>
-    <t>Fe2O3</t>
-  </si>
-  <si>
-    <t>MgO</t>
-  </si>
-  <si>
-    <t>MnO2</t>
-  </si>
-  <si>
-    <t>NiO</t>
-  </si>
-  <si>
-    <t>SiO2</t>
-  </si>
-  <si>
-    <t>SnO2</t>
-  </si>
-  <si>
-    <t>TiO2</t>
-  </si>
-  <si>
-    <t>V2O5</t>
-  </si>
-  <si>
-    <t>ZnO</t>
-  </si>
-  <si>
-    <t>CFRP</t>
-  </si>
-  <si>
-    <t>[50,55]</t>
-  </si>
-  <si>
-    <t>[55,60]</t>
-  </si>
-  <si>
-    <t>[60,65]</t>
-  </si>
-  <si>
-    <t>[65,70]</t>
-  </si>
-  <si>
-    <t>REAT</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Zn</t>
-  </si>
-  <si>
-    <t>Mg2</t>
-  </si>
-  <si>
-    <t>NO2</t>
-  </si>
-  <si>
-    <t>[45,50]</t>
-  </si>
-  <si>
-    <t>Mn</t>
-  </si>
-  <si>
-    <t>[35,40]</t>
-  </si>
-  <si>
-    <t>[40,45]</t>
-  </si>
-  <si>
-    <t>V4O10</t>
-  </si>
-  <si>
-    <t>Cl</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>OH</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>CH4</t>
-  </si>
-  <si>
-    <t>CLO</t>
-  </si>
-  <si>
-    <t>HCl</t>
-  </si>
-  <si>
-    <t>HCN</t>
-  </si>
-  <si>
-    <t>HNC</t>
-  </si>
-  <si>
-    <t>HOCL</t>
-  </si>
-  <si>
-    <t>NH3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000000"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00000000000000"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00000000000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -270,7 +464,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -404,11 +598,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC6C6C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC6C6C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC6C6C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -461,48 +670,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -513,6 +680,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -818,33 +996,33 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BR55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="22" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.6640625" style="33" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.6640625" style="33" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" style="33" customWidth="1"/>
-    <col min="14" max="16" width="10.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="10.6640625" style="33" customWidth="1"/>
-    <col min="19" max="19" width="10.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="10.6640625" style="34" customWidth="1"/>
-    <col min="24" max="24" width="10.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.6640625" style="34" customWidth="1"/>
-    <col min="27" max="27" width="10.6640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="10.6640625" style="34" customWidth="1"/>
-    <col min="31" max="32" width="10.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="8.33203125" customWidth="1"/>
-    <col min="40" max="40" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.7109375" style="19" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.7109375" style="19" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" style="19" customWidth="1"/>
+    <col min="14" max="16" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10.7109375" style="19" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="10.7109375" style="20" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7109375" style="20" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="10.7109375" style="20" customWidth="1"/>
+    <col min="31" max="32" width="10.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="8.28515625" customWidth="1"/>
+    <col min="43" max="43" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>8</v>
       </c>
@@ -858,117 +1036,207 @@
         <v>11</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U1" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="X1" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD1" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG1" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ1" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK1" s="13" t="s">
+      <c r="AL1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AL1" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="AM1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="AN1" s="13" t="s">
-        <v>12</v>
+        <v>44</v>
+      </c>
+      <c r="AN1" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO1" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP1" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ1" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR1" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AS1" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT1" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU1" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AV1" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="AW1" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX1" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY1" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AZ1" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="BA1" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="BB1" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC1" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD1" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="BE1" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="BF1" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="BG1" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="BH1" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BI1" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="BJ1" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK1" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL1" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="BM1" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="BN1" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO1" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP1" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ1" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="BR1" s="25" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:70" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>13</v>
@@ -980,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="16">
-        <v>0.1133728687916975</v>
+        <v>0</v>
       </c>
       <c r="F2" s="16">
         <v>0</v>
@@ -988,7 +1256,7 @@
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
       <c r="I2" s="16">
-        <v>0</v>
+        <v>7.328282407792857E-3</v>
       </c>
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
@@ -997,13 +1265,13 @@
       </c>
       <c r="M2" s="16"/>
       <c r="N2" s="16">
-        <v>0</v>
+        <v>0.36538868374490352</v>
       </c>
       <c r="O2" s="16">
         <v>0</v>
       </c>
       <c r="P2" s="16">
-        <v>0</v>
+        <v>0.7263094636941535</v>
       </c>
       <c r="Q2" s="16"/>
       <c r="R2" s="16"/>
@@ -1020,24 +1288,24 @@
       <c r="Y2" s="16"/>
       <c r="Z2" s="16"/>
       <c r="AA2" s="16">
-        <v>0</v>
+        <v>3.165022388874731E-2</v>
       </c>
       <c r="AB2" s="16">
-        <v>0</v>
+        <v>0.25451075937505319</v>
       </c>
       <c r="AC2" s="16"/>
       <c r="AD2" s="16"/>
       <c r="AE2" s="16">
-        <v>0</v>
+        <v>4.2784404486380628E-2</v>
       </c>
       <c r="AF2" s="16">
         <v>0</v>
       </c>
       <c r="AG2" s="16">
-        <v>1.5016294129935239</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="17">
-        <v>7.1409501374165685E-2</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="17"/>
       <c r="AJ2" s="17">
@@ -1047,10 +1315,14 @@
       <c r="AL2" s="17"/>
       <c r="AM2" s="17"/>
       <c r="AN2" s="17"/>
+      <c r="AO2" s="17"/>
+      <c r="AP2" s="17"/>
+      <c r="AQ2" s="17"/>
+      <c r="BR2" s="26"/>
     </row>
-    <row r="3" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>13</v>
@@ -1059,30 +1331,30 @@
         <v>15</v>
       </c>
       <c r="D3" s="16">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="16">
-        <v>0</v>
+        <v>1.7584890426951301</v>
       </c>
       <c r="F3" s="16">
-        <v>0</v>
+        <v>6.4449485575915804E-3</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
       <c r="I3" s="16">
-        <v>3.349303913405496</v>
+        <v>0</v>
       </c>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
       <c r="L3" s="16">
-        <v>1.3100000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="16"/>
       <c r="N3" s="16">
         <v>0</v>
       </c>
       <c r="O3" s="16">
-        <v>0</v>
+        <v>5.3829509331822623E-2</v>
       </c>
       <c r="P3" s="16">
         <v>0</v>
@@ -1090,14 +1362,14 @@
       <c r="Q3" s="16"/>
       <c r="R3" s="16"/>
       <c r="S3" s="16">
-        <v>0.2073730158730159</v>
+        <v>0</v>
       </c>
       <c r="T3" s="16"/>
       <c r="U3" s="16"/>
       <c r="V3" s="16"/>
       <c r="W3" s="16"/>
       <c r="X3" s="16">
-        <v>0</v>
+        <v>1.3264760337379141E-2</v>
       </c>
       <c r="Y3" s="16"/>
       <c r="Z3" s="16"/>
@@ -1110,29 +1382,37 @@
       <c r="AC3" s="16"/>
       <c r="AD3" s="16"/>
       <c r="AE3" s="16">
-        <v>0</v>
+        <v>2.567064269182837E-3</v>
       </c>
       <c r="AF3" s="16">
-        <v>0</v>
+        <v>3.1739112121977929E-3</v>
       </c>
       <c r="AG3" s="16">
-        <v>0</v>
+        <v>1.6684981302358621E-3</v>
       </c>
       <c r="AH3" s="17">
         <v>0</v>
       </c>
       <c r="AI3" s="17"/>
       <c r="AJ3" s="17">
-        <v>0</v>
+        <v>1.991557051085959E-3</v>
       </c>
       <c r="AK3" s="17"/>
-      <c r="AL3" s="17"/>
-      <c r="AM3" s="17"/>
+      <c r="AL3" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="17">
+        <v>0</v>
+      </c>
       <c r="AN3" s="17"/>
+      <c r="AO3" s="17"/>
+      <c r="AP3" s="17"/>
+      <c r="AQ3" s="17"/>
+      <c r="BR3" s="26"/>
     </row>
-    <row r="4" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>13</v>
@@ -1144,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="16">
-        <v>1.7440526315789471</v>
+        <v>1.7622678952635089</v>
       </c>
       <c r="F4" s="16">
-        <v>0</v>
+        <v>6.4449485575915804E-3</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -1161,13 +1441,13 @@
       </c>
       <c r="M4" s="16"/>
       <c r="N4" s="16">
-        <v>0</v>
+        <v>7.3077736748980698E-4</v>
       </c>
       <c r="O4" s="16">
-        <v>8.5120377655389462E-2</v>
+        <v>4.3814716897995147E-2</v>
       </c>
       <c r="P4" s="16">
-        <v>4.2891674127126219E-3</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="16"/>
       <c r="R4" s="16"/>
@@ -1179,12 +1459,12 @@
       <c r="V4" s="16"/>
       <c r="W4" s="16"/>
       <c r="X4" s="16">
-        <v>0</v>
+        <v>1.3264760337379141E-2</v>
       </c>
       <c r="Y4" s="16"/>
       <c r="Z4" s="16"/>
       <c r="AA4" s="16">
-        <v>6.3298143429195482E-3</v>
+        <v>7.9125559721868275E-3</v>
       </c>
       <c r="AB4" s="16">
         <v>0</v>
@@ -1192,29 +1472,37 @@
       <c r="AC4" s="16"/>
       <c r="AD4" s="16"/>
       <c r="AE4" s="16">
-        <v>0</v>
+        <v>1.7113761794552249E-3</v>
       </c>
       <c r="AF4" s="16">
-        <v>0</v>
+        <v>3.1739112121977929E-3</v>
       </c>
       <c r="AG4" s="16">
-        <v>0</v>
+        <v>1.6684981302358621E-3</v>
       </c>
       <c r="AH4" s="17">
         <v>0</v>
       </c>
       <c r="AI4" s="17"/>
       <c r="AJ4" s="17">
-        <v>0</v>
+        <v>4.3565310492505354E-3</v>
       </c>
       <c r="AK4" s="17"/>
-      <c r="AL4" s="17"/>
-      <c r="AM4" s="17"/>
+      <c r="AL4" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="17">
+        <v>0</v>
+      </c>
       <c r="AN4" s="17"/>
+      <c r="AO4" s="17"/>
+      <c r="AP4" s="17"/>
+      <c r="AQ4" s="17"/>
+      <c r="BR4" s="26"/>
     </row>
-    <row r="5" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>13</v>
@@ -1226,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="16">
-        <v>0</v>
+        <v>1.7439404603068711</v>
       </c>
       <c r="F5" s="16">
         <v>0</v>
@@ -1234,7 +1522,7 @@
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
       <c r="I5" s="16">
-        <v>7.3288925895087431E-3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
@@ -1243,13 +1531,13 @@
       </c>
       <c r="M5" s="16"/>
       <c r="N5" s="16">
-        <v>0.36543085208693982</v>
+        <v>0</v>
       </c>
       <c r="O5" s="16">
-        <v>0</v>
+        <v>8.5125735687533455E-2</v>
       </c>
       <c r="P5" s="16">
-        <v>0.72629901521933748</v>
+        <v>4.2892291163040561E-3</v>
       </c>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
@@ -1266,15 +1554,15 @@
       <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
       <c r="AA5" s="16">
-        <v>3.1649071714597743E-2</v>
+        <v>6.3300447777494629E-3</v>
       </c>
       <c r="AB5" s="16">
-        <v>0.25452376895552897</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="16"/>
       <c r="AE5" s="16">
-        <v>4.277678889284442E-2</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="16">
         <v>0</v>
@@ -1293,10 +1581,14 @@
       <c r="AL5" s="17"/>
       <c r="AM5" s="17"/>
       <c r="AN5" s="17"/>
+      <c r="AO5" s="17"/>
+      <c r="AP5" s="17"/>
+      <c r="AQ5" s="17"/>
+      <c r="BR5" s="26"/>
     </row>
-    <row r="6" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>13</v>
@@ -1308,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="16">
-        <v>1.109164566345441</v>
+        <v>1.7892866911274179</v>
       </c>
       <c r="F6" s="16">
         <v>0</v>
@@ -1325,13 +1617,13 @@
       </c>
       <c r="M6" s="16"/>
       <c r="N6" s="16">
-        <v>1.4617234083477591E-3</v>
+        <v>0</v>
       </c>
       <c r="O6" s="16">
         <v>0</v>
       </c>
       <c r="P6" s="16">
-        <v>0</v>
+        <v>5.7189721550720742E-3</v>
       </c>
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
@@ -1343,7 +1635,7 @@
       <c r="V6" s="16"/>
       <c r="W6" s="16"/>
       <c r="X6" s="16">
-        <v>2.321431509666803E-2</v>
+        <v>9.2853322361653987E-2</v>
       </c>
       <c r="Y6" s="16"/>
       <c r="Z6" s="16"/>
@@ -1359,26 +1651,30 @@
         <v>0</v>
       </c>
       <c r="AF6" s="16">
-        <v>1.142608036391206E-2</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="16">
-        <v>0.56394526843534576</v>
+        <v>0</v>
       </c>
       <c r="AH6" s="17">
-        <v>2.6778563015312139E-2</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="17"/>
       <c r="AJ6" s="17">
-        <v>4.4810033649434089E-2</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="17"/>
       <c r="AL6" s="17"/>
       <c r="AM6" s="17"/>
       <c r="AN6" s="17"/>
+      <c r="AO6" s="17"/>
+      <c r="AP6" s="17"/>
+      <c r="AQ6" s="17"/>
+      <c r="BR6" s="26"/>
     </row>
-    <row r="7" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>13</v>
@@ -1390,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="16">
-        <v>1.7733406226834689</v>
+        <v>1.6498470313542359</v>
       </c>
       <c r="F7" s="16">
-        <v>3.2224900343005469E-3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -1407,13 +1703,13 @@
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="16">
-        <v>0</v>
+        <v>4.0923532579429187E-3</v>
       </c>
       <c r="O7" s="16">
-        <v>4.1308418568056643E-2</v>
+        <v>2.5036981084568651E-2</v>
       </c>
       <c r="P7" s="16">
-        <v>0</v>
+        <v>7.1487151938400923E-3</v>
       </c>
       <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
@@ -1425,12 +1721,12 @@
       <c r="V7" s="16"/>
       <c r="W7" s="16"/>
       <c r="X7" s="16">
-        <v>1.160715754833402E-2</v>
+        <v>4.8084756222999382E-2</v>
       </c>
       <c r="Y7" s="16"/>
       <c r="Z7" s="16"/>
       <c r="AA7" s="16">
-        <v>7.9122679286494357E-3</v>
+        <v>4.7475335833120974E-3</v>
       </c>
       <c r="AB7" s="16">
         <v>0</v>
@@ -1438,407 +1734,612 @@
       <c r="AC7" s="16"/>
       <c r="AD7" s="16"/>
       <c r="AE7" s="16">
-        <v>0</v>
+        <v>8.5568808972761243E-3</v>
       </c>
       <c r="AF7" s="16">
         <v>0</v>
       </c>
       <c r="AG7" s="16">
-        <v>0</v>
+        <v>3.3369962604717241E-3</v>
       </c>
       <c r="AH7" s="17">
         <v>0</v>
       </c>
       <c r="AI7" s="17"/>
       <c r="AJ7" s="17">
-        <v>4.3565310492505336E-3</v>
+        <v>7.5928112572652182E-2</v>
       </c>
       <c r="AK7" s="17"/>
-      <c r="AL7" s="17"/>
-      <c r="AM7" s="17"/>
+      <c r="AL7" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="17">
+        <v>0</v>
+      </c>
       <c r="AN7" s="17"/>
+      <c r="AO7" s="17"/>
+      <c r="AP7" s="17"/>
+      <c r="AQ7" s="17"/>
+      <c r="BR7" s="26"/>
     </row>
-    <row r="8" spans="1:40" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0</v>
+      </c>
       <c r="E8" s="16">
-        <v>1.747483147333333</v>
-      </c>
-      <c r="F8" s="16"/>
+        <v>1.109093228819213</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0</v>
+      </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
+      <c r="I8" s="16">
+        <v>0</v>
+      </c>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
+      <c r="L8" s="16">
+        <v>0</v>
+      </c>
       <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
+      <c r="N8" s="16">
+        <v>1.461554734979614E-3</v>
+      </c>
       <c r="O8" s="16">
-        <v>8.5290871000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="16">
-        <v>4.2978019999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
+      <c r="S8" s="16">
+        <v>0</v>
+      </c>
       <c r="T8" s="16"/>
       <c r="U8" s="16"/>
       <c r="V8" s="16"/>
       <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
+      <c r="X8" s="16">
+        <v>2.32133305904135E-2</v>
+      </c>
       <c r="Y8" s="16"/>
-      <c r="Z8" s="16">
-        <v>3.651418E-3</v>
-      </c>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="16">
+        <v>0</v>
+      </c>
       <c r="AC8" s="16"/>
       <c r="AD8" s="16"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="17"/>
+      <c r="AE8" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="16">
+        <v>1.142608036391205E-2</v>
+      </c>
+      <c r="AG8" s="16">
+        <v>0.56395236801972137</v>
+      </c>
+      <c r="AH8" s="17">
+        <v>2.677751167994975E-2</v>
+      </c>
       <c r="AI8" s="17"/>
-      <c r="AJ8" s="17"/>
+      <c r="AJ8" s="17">
+        <v>4.4810033649434082E-2</v>
+      </c>
       <c r="AK8" s="17"/>
-      <c r="AL8" s="17">
-        <v>1.0006082666666669E-2</v>
-      </c>
-      <c r="AM8" s="17">
-        <v>8.2960233333333332E-5</v>
-      </c>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="17"/>
       <c r="AN8" s="17"/>
+      <c r="AO8" s="17"/>
+      <c r="AP8" s="17"/>
+      <c r="AQ8" s="17"/>
+      <c r="BR8" s="26"/>
     </row>
-    <row r="9" spans="1:40" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="D9" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="E9" s="16">
-        <v>1.7474676012499999</v>
-      </c>
-      <c r="F9" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="16">
+        <v>0</v>
+      </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+      <c r="I9" s="16">
+        <v>3.3490250603613361</v>
+      </c>
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
+      <c r="L9" s="16">
+        <v>1.3100000000000001E-2</v>
+      </c>
       <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
+      <c r="N9" s="16">
+        <v>0</v>
+      </c>
       <c r="O9" s="16">
-        <v>8.5291162900000009E-2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="16">
-        <v>4.2978489499999996E-3</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
+      <c r="S9" s="16">
+        <v>0.20731547619047619</v>
+      </c>
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
       <c r="V9" s="16"/>
       <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
+      <c r="X9" s="16">
+        <v>0</v>
+      </c>
       <c r="Y9" s="16"/>
-      <c r="Z9" s="16">
-        <v>3.6948376499999999E-3</v>
-      </c>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="16">
+        <v>0</v>
+      </c>
       <c r="AC9" s="16"/>
       <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="17"/>
+      <c r="AE9" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="17">
+        <v>0</v>
+      </c>
       <c r="AI9" s="17"/>
-      <c r="AJ9" s="17"/>
+      <c r="AJ9" s="17">
+        <v>0</v>
+      </c>
       <c r="AK9" s="17"/>
       <c r="AL9" s="17">
-        <v>3.5342942350000003E-2</v>
+        <v>5.7847504819019062E-2</v>
       </c>
       <c r="AM9" s="17">
-        <v>2.2061107300000001E-4</v>
+        <v>8.8689226815163835E-2</v>
       </c>
       <c r="AN9" s="17"/>
+      <c r="AO9" s="17"/>
+      <c r="AP9" s="17"/>
+      <c r="AQ9" s="17"/>
+      <c r="BR9" s="26"/>
     </row>
-    <row r="10" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="D10" s="16">
+        <v>0</v>
+      </c>
       <c r="E10" s="16">
-        <v>1.747467276314286</v>
-      </c>
-      <c r="F10" s="16"/>
+        <v>0.85307596731154101</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0</v>
+      </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
+      <c r="I10" s="16">
+        <v>1.674512530180668</v>
+      </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
+      <c r="L10" s="16" t="e">
+        <f>0.5*#REF!</f>
+        <v>#REF!</v>
+      </c>
       <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
+      <c r="N10" s="16">
+        <v>1.6077102084775751E-3</v>
+      </c>
       <c r="O10" s="16">
-        <v>8.529121837142857E-2</v>
+        <v>0</v>
       </c>
       <c r="P10" s="16">
-        <v>4.2978311714285712E-3</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
+      <c r="S10" s="16">
+        <v>0.10365773809523809</v>
+      </c>
       <c r="T10" s="16"/>
       <c r="U10" s="16"/>
       <c r="V10" s="16"/>
       <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
+      <c r="X10" s="16">
+        <v>1.9068092984982511E-2</v>
+      </c>
       <c r="Y10" s="16"/>
-      <c r="Z10" s="16">
-        <v>3.9622456857142854E-3</v>
-      </c>
-      <c r="AA10" s="16"/>
-      <c r="AB10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="16">
+        <v>0</v>
+      </c>
       <c r="AC10" s="16"/>
       <c r="AD10" s="16"/>
-      <c r="AE10" s="16"/>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="17"/>
+      <c r="AE10" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="16">
+        <v>9.5217336365933797E-3</v>
+      </c>
+      <c r="AG10" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="17">
+        <v>0</v>
+      </c>
       <c r="AI10" s="17"/>
-      <c r="AJ10" s="17"/>
+      <c r="AJ10" s="17">
+        <v>3.5474609972468638E-2</v>
+      </c>
       <c r="AK10" s="17"/>
       <c r="AL10" s="17">
-        <v>4.9158257142857141E-4</v>
+        <v>2.8923752409509531E-2</v>
       </c>
       <c r="AM10" s="17">
-        <v>2.537401942857142E-6</v>
+        <v>4.4344613407581918E-2</v>
       </c>
       <c r="AN10" s="17"/>
+      <c r="AO10" s="17"/>
+      <c r="AP10" s="17"/>
+      <c r="AQ10" s="17"/>
+      <c r="BR10" s="26"/>
     </row>
-    <row r="11" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
       <c r="E11" s="16">
-        <v>1.7474725788800001</v>
-      </c>
-      <c r="F11" s="16"/>
+        <v>1.511541027351568E-2</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0</v>
+      </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
+      <c r="I11" s="16">
+        <v>2.931312963117143E-3</v>
+      </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
+      <c r="L11" s="16">
+        <v>0</v>
+      </c>
       <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
+      <c r="N11" s="16">
+        <v>0.30692649434571889</v>
+      </c>
       <c r="O11" s="16">
-        <v>8.5291370679999992E-2</v>
+        <v>3.755547162685299E-3</v>
       </c>
       <c r="P11" s="16">
-        <v>4.29782064E-3</v>
+        <v>0.1689956271823797</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
+      <c r="S11" s="16">
+        <v>0</v>
+      </c>
       <c r="T11" s="16"/>
       <c r="U11" s="16"/>
       <c r="V11" s="16"/>
       <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
+      <c r="X11" s="16">
+        <v>0</v>
+      </c>
       <c r="Y11" s="16"/>
-      <c r="Z11" s="16">
-        <v>3.9859451600000014E-3</v>
-      </c>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="16">
+        <v>0.69990458828139634</v>
+      </c>
       <c r="AC11" s="16"/>
       <c r="AD11" s="16"/>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="17"/>
+      <c r="AE11" s="16">
+        <v>7.4872707851166096E-3</v>
+      </c>
+      <c r="AF11" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="16">
+        <v>1.9187728497712411E-2</v>
+      </c>
+      <c r="AH11" s="17">
+        <v>0</v>
+      </c>
       <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
+      <c r="AJ11" s="17">
+        <v>0</v>
+      </c>
       <c r="AK11" s="17"/>
-      <c r="AL11" s="17">
-        <v>1.112266E-4</v>
-      </c>
-      <c r="AM11" s="17">
-        <v>3.8265572E-7</v>
-      </c>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
       <c r="AN11" s="17"/>
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="17"/>
+      <c r="AQ11" s="17"/>
+      <c r="BR11" s="26"/>
     </row>
-    <row r="12" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:70" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0</v>
+      </c>
       <c r="E12" s="16">
-        <v>1.7474571990000001</v>
-      </c>
-      <c r="F12" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="16">
+        <v>1.0741580929319299E-2</v>
+      </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
+      <c r="I12" s="16">
+        <v>0</v>
+      </c>
       <c r="J12" s="16"/>
       <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
+      <c r="L12" s="16">
+        <v>0</v>
+      </c>
       <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
+      <c r="N12" s="16">
+        <v>0</v>
+      </c>
       <c r="O12" s="16">
-        <v>8.5291107777777764E-2</v>
+        <v>0.3880732068108142</v>
       </c>
       <c r="P12" s="16">
-        <v>4.2978444444444451E-3</v>
+        <v>0.22875888620288301</v>
       </c>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
+      <c r="S12" s="16">
+        <v>0</v>
+      </c>
       <c r="T12" s="16"/>
       <c r="U12" s="16"/>
       <c r="V12" s="16"/>
       <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
+      <c r="X12" s="16">
+        <v>0</v>
+      </c>
       <c r="Y12" s="16"/>
-      <c r="Z12" s="16">
-        <v>3.9874198888888886E-3</v>
-      </c>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="16">
+        <v>0.26723629734380588</v>
+      </c>
       <c r="AC12" s="16"/>
       <c r="AD12" s="16"/>
-      <c r="AE12" s="16"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="17"/>
+      <c r="AE12" s="16">
+        <v>0.66315826953889978</v>
+      </c>
+      <c r="AF12" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="17">
+        <v>0</v>
+      </c>
       <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
+      <c r="AJ12" s="17">
+        <v>0</v>
+      </c>
       <c r="AK12" s="17"/>
       <c r="AL12" s="17">
-        <v>5.318087777777778E-5</v>
+        <v>0</v>
       </c>
       <c r="AM12" s="17">
-        <v>1.2422499999999999E-7</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="17"/>
+      <c r="AO12" s="17"/>
+      <c r="AP12" s="17"/>
+      <c r="AQ12" s="17"/>
+      <c r="AR12" s="24"/>
+      <c r="AS12" s="24"/>
+      <c r="AT12" s="24"/>
+      <c r="AU12" s="24"/>
+      <c r="AV12" s="24"/>
+      <c r="AW12" s="24"/>
+      <c r="AX12" s="24"/>
+      <c r="AY12" s="24"/>
+      <c r="AZ12" s="24"/>
+      <c r="BA12" s="24"/>
+      <c r="BB12" s="24"/>
+      <c r="BC12" s="24"/>
+      <c r="BD12" s="24"/>
+      <c r="BE12" s="24"/>
+      <c r="BF12" s="24"/>
+      <c r="BG12" s="24"/>
+      <c r="BH12" s="24"/>
+      <c r="BI12" s="24"/>
+      <c r="BR12" s="26"/>
     </row>
-    <row r="13" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="D13" s="16">
+        <v>0</v>
+      </c>
       <c r="E13" s="16">
-        <v>1.1091141229999999</v>
-      </c>
-      <c r="F13" s="16"/>
+        <v>0.1133655770513676</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
+      <c r="I13" s="16">
+        <v>0</v>
+      </c>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
+      <c r="L13" s="16">
+        <v>0</v>
+      </c>
       <c r="M13" s="16"/>
       <c r="N13" s="16">
-        <v>1.4615107999999999E-3</v>
-      </c>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="16">
+        <v>0</v>
+      </c>
+      <c r="P13" s="16">
+        <v>0</v>
+      </c>
       <c r="Q13" s="16"/>
       <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
+      <c r="S13" s="16">
+        <v>0</v>
+      </c>
       <c r="T13" s="16"/>
       <c r="U13" s="16"/>
       <c r="V13" s="16"/>
       <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16">
-        <v>3.3593184600000013E-2</v>
-      </c>
+      <c r="X13" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
+      <c r="AA13" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="16">
+        <v>0</v>
+      </c>
       <c r="AC13" s="16"/>
       <c r="AD13" s="16"/>
-      <c r="AE13" s="16"/>
+      <c r="AE13" s="16">
+        <v>0</v>
+      </c>
       <c r="AF13" s="16">
-        <v>1.14260218E-2</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="16">
-        <v>0.56395642199999996</v>
+        <v>1.5016483172122761</v>
       </c>
       <c r="AH13" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="17">
-        <v>2.6777834E-2</v>
-      </c>
-      <c r="AJ13" s="17"/>
-      <c r="AK13" s="17">
-        <v>3.5999945399999997E-2</v>
-      </c>
-      <c r="AL13" s="17">
-        <v>2.67050458E-2</v>
-      </c>
-      <c r="AM13" s="17">
-        <v>4.4454953999999999E-4</v>
-      </c>
+        <v>7.1406697813199332E-2</v>
+      </c>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
       <c r="AN13" s="17"/>
+      <c r="AO13" s="17"/>
+      <c r="AP13" s="17"/>
+      <c r="AQ13" s="17"/>
+      <c r="AR13" s="24"/>
+      <c r="AS13" s="24"/>
+      <c r="AT13" s="24"/>
+      <c r="AU13" s="24"/>
+      <c r="AV13" s="24"/>
+      <c r="AW13" s="24"/>
+      <c r="AX13" s="24"/>
+      <c r="AY13" s="24"/>
+      <c r="AZ13" s="24"/>
+      <c r="BA13" s="24"/>
+      <c r="BB13" s="24"/>
+      <c r="BC13" s="24"/>
+      <c r="BD13" s="24"/>
+      <c r="BE13" s="24"/>
+      <c r="BF13" s="24"/>
+      <c r="BG13" s="24"/>
+      <c r="BH13" s="24"/>
+      <c r="BI13" s="24"/>
+      <c r="BR13" s="26"/>
     </row>
-    <row r="14" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="16">
-        <v>1.1091178045000001</v>
+        <v>1.747483147333333</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
@@ -1848,11 +2349,13 @@
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
-      <c r="N14" s="16">
-        <v>1.461552625E-3</v>
-      </c>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16">
+        <v>8.5290871000000004E-2</v>
+      </c>
+      <c r="P14" s="16">
+        <v>4.2978019999999999E-3</v>
+      </c>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
@@ -1861,52 +2364,64 @@
       <c r="V14" s="16"/>
       <c r="W14" s="16"/>
       <c r="X14" s="16"/>
-      <c r="Y14" s="16">
-        <v>3.3592747375000002E-2</v>
-      </c>
-      <c r="Z14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16">
+        <v>3.651418E-3</v>
+      </c>
       <c r="AA14" s="16"/>
       <c r="AB14" s="16"/>
       <c r="AC14" s="16"/>
       <c r="AD14" s="16"/>
       <c r="AE14" s="16"/>
-      <c r="AF14" s="16">
-        <v>1.1425976062500001E-2</v>
-      </c>
-      <c r="AG14" s="16">
-        <v>0.56395131249999997</v>
-      </c>
-      <c r="AH14" s="17">
-        <v>1.14246734375E-2</v>
-      </c>
-      <c r="AI14" s="17">
-        <v>1.5596421875E-2</v>
-      </c>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="17"/>
       <c r="AJ14" s="17"/>
-      <c r="AK14" s="17">
-        <v>3.5999904625000002E-2</v>
-      </c>
+      <c r="AK14" s="17"/>
       <c r="AL14" s="17">
-        <v>1.6146733124999999E-3</v>
+        <v>1.0006082666666669E-2</v>
       </c>
       <c r="AM14" s="17">
-        <v>2.2330789999999999E-5</v>
+        <v>8.2960233333333332E-5</v>
       </c>
       <c r="AN14" s="17"/>
+      <c r="AO14" s="17"/>
+      <c r="AP14" s="17"/>
+      <c r="AQ14" s="17"/>
+      <c r="AR14" s="17"/>
+      <c r="AS14" s="17"/>
+      <c r="AT14" s="17"/>
+      <c r="AU14" s="17"/>
+      <c r="AV14" s="17"/>
+      <c r="AW14" s="17"/>
+      <c r="AX14" s="17"/>
+      <c r="AY14" s="17"/>
+      <c r="AZ14" s="17"/>
+      <c r="BA14" s="17"/>
+      <c r="BB14" s="17"/>
+      <c r="BC14" s="17"/>
+      <c r="BD14" s="17"/>
+      <c r="BE14" s="17"/>
+      <c r="BF14" s="17"/>
+      <c r="BG14" s="17"/>
+      <c r="BH14" s="17"/>
+      <c r="BI14" s="17"/>
+      <c r="BR14" s="26"/>
     </row>
-    <row r="15" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:70" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16">
-        <v>1.109113873133333</v>
+        <v>1.7474676012499999</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
@@ -1916,11 +2431,13 @@
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
-      <c r="N15" s="16">
-        <v>1.4615562E-3</v>
-      </c>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16">
+        <v>8.5291162900000009E-2</v>
+      </c>
+      <c r="P15" s="16">
+        <v>4.2978489499999996E-3</v>
+      </c>
       <c r="Q15" s="16"/>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
@@ -1929,52 +2446,64 @@
       <c r="V15" s="16"/>
       <c r="W15" s="16"/>
       <c r="X15" s="16"/>
-      <c r="Y15" s="16">
-        <v>3.3592821333333328E-2</v>
-      </c>
-      <c r="Z15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16">
+        <v>3.6948376499999999E-3</v>
+      </c>
       <c r="AA15" s="16"/>
       <c r="AB15" s="16"/>
       <c r="AC15" s="16"/>
       <c r="AD15" s="16"/>
       <c r="AE15" s="16"/>
-      <c r="AF15" s="16">
-        <v>1.142605153333333E-2</v>
-      </c>
-      <c r="AG15" s="16">
-        <v>0.56395108459999999</v>
-      </c>
-      <c r="AH15" s="17">
-        <v>2.110228006666667E-2</v>
-      </c>
-      <c r="AI15" s="17">
-        <v>5.6754625333333341E-3</v>
-      </c>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
       <c r="AJ15" s="17"/>
-      <c r="AK15" s="17">
-        <v>3.6000157400000003E-2</v>
-      </c>
+      <c r="AK15" s="17"/>
       <c r="AL15" s="17">
-        <v>2.74166E-4</v>
+        <v>3.5342942350000003E-2</v>
       </c>
       <c r="AM15" s="17">
-        <v>2.6206906666666662E-6</v>
+        <v>2.2061107300000001E-4</v>
       </c>
       <c r="AN15" s="17"/>
+      <c r="AO15" s="17"/>
+      <c r="AP15" s="17"/>
+      <c r="AQ15" s="17"/>
+      <c r="AR15" s="17"/>
+      <c r="AS15" s="17"/>
+      <c r="AT15" s="17"/>
+      <c r="AU15" s="17"/>
+      <c r="AV15" s="17"/>
+      <c r="AW15" s="17"/>
+      <c r="AX15" s="17"/>
+      <c r="AY15" s="17"/>
+      <c r="AZ15" s="17"/>
+      <c r="BA15" s="17"/>
+      <c r="BB15" s="17"/>
+      <c r="BC15" s="17"/>
+      <c r="BD15" s="17"/>
+      <c r="BE15" s="17"/>
+      <c r="BF15" s="17"/>
+      <c r="BG15" s="17"/>
+      <c r="BH15" s="17"/>
+      <c r="BI15" s="17"/>
+      <c r="BR15" s="26"/>
     </row>
-    <row r="16" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:70" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16">
-        <v>1.1091168203571431</v>
+        <v>1.747467276314286</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
@@ -1984,11 +2513,13 @@
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
-      <c r="N16" s="16">
-        <v>1.4615561428571429E-3</v>
-      </c>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16">
+        <v>8.529121837142857E-2</v>
+      </c>
+      <c r="P16" s="16">
+        <v>4.2978311714285712E-3</v>
+      </c>
       <c r="Q16" s="16"/>
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
@@ -1997,108 +2528,96 @@
       <c r="V16" s="16"/>
       <c r="W16" s="16"/>
       <c r="X16" s="16"/>
-      <c r="Y16" s="16">
-        <v>3.3593201928571431E-2</v>
-      </c>
-      <c r="Z16" s="16"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16">
+        <v>3.9622456857142854E-3</v>
+      </c>
       <c r="AA16" s="16"/>
       <c r="AB16" s="16"/>
       <c r="AC16" s="16"/>
       <c r="AD16" s="16"/>
       <c r="AE16" s="16"/>
-      <c r="AF16" s="16">
-        <v>1.142599314285714E-2</v>
-      </c>
-      <c r="AG16" s="16">
-        <v>0.56395060885714288</v>
-      </c>
-      <c r="AH16" s="17">
-        <v>2.220479978571429E-2</v>
-      </c>
-      <c r="AI16" s="17">
-        <v>4.5732168571428564E-3</v>
-      </c>
+      <c r="AF16" s="16"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="17"/>
       <c r="AJ16" s="17"/>
-      <c r="AK16" s="17">
-        <v>3.5999876714285707E-2</v>
-      </c>
+      <c r="AK16" s="17"/>
       <c r="AL16" s="17">
-        <v>1.112760285714286E-4</v>
+        <v>4.9158257142857141E-4</v>
       </c>
       <c r="AM16" s="17">
-        <v>7.3929299999999997E-7</v>
+        <v>2.537401942857142E-6</v>
       </c>
       <c r="AN16" s="17"/>
+      <c r="AO16" s="17"/>
+      <c r="AP16" s="17"/>
+      <c r="AQ16" s="17"/>
+      <c r="AR16" s="17"/>
+      <c r="AS16" s="17"/>
+      <c r="AT16" s="17"/>
+      <c r="AU16" s="17"/>
+      <c r="AV16" s="17"/>
+      <c r="AW16" s="17"/>
+      <c r="AX16" s="17"/>
+      <c r="AY16" s="17"/>
+      <c r="AZ16" s="17"/>
+      <c r="BA16" s="17"/>
+      <c r="BB16" s="17"/>
+      <c r="BC16" s="17"/>
+      <c r="BD16" s="17"/>
+      <c r="BE16" s="17"/>
+      <c r="BF16" s="17"/>
+      <c r="BG16" s="17"/>
+      <c r="BH16" s="17"/>
+      <c r="BI16" s="17"/>
+      <c r="BR16" s="26"/>
     </row>
-    <row r="17" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="E17" s="16">
+        <v>1.7474725788800001</v>
+      </c>
       <c r="F17" s="16"/>
-      <c r="G17" s="16">
-        <v>0</v>
-      </c>
-      <c r="H17" s="16">
-        <v>0</v>
-      </c>
-      <c r="I17" s="16">
-        <v>3.350000000000001</v>
-      </c>
-      <c r="J17" s="16">
-        <v>0</v>
-      </c>
-      <c r="K17" s="16">
-        <v>1.2222857142857139E-4</v>
-      </c>
-      <c r="L17" s="16">
-        <v>3.107142857142857E-6</v>
-      </c>
-      <c r="M17" s="16">
-        <v>7.8757142857142862E-8</v>
-      </c>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
       <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16">
-        <v>0</v>
-      </c>
-      <c r="R17" s="16">
-        <v>0</v>
-      </c>
-      <c r="S17" s="16">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="T17" s="16">
-        <v>1.3342857142857141E-2</v>
-      </c>
-      <c r="U17" s="16">
-        <v>0</v>
-      </c>
-      <c r="V17" s="16">
-        <v>0</v>
-      </c>
-      <c r="W17" s="16">
-        <v>1.7242857142857141E-8</v>
-      </c>
+      <c r="O17" s="16">
+        <v>8.5291370679999992E-2</v>
+      </c>
+      <c r="P17" s="16">
+        <v>4.29782064E-3</v>
+      </c>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
       <c r="X17" s="16"/>
       <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
+      <c r="Z17" s="16">
+        <v>3.9859451600000014E-3</v>
+      </c>
       <c r="AA17" s="16"/>
       <c r="AB17" s="16"/>
-      <c r="AC17" s="16">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="16">
-        <v>3.0599999999999999E-6</v>
-      </c>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
       <c r="AE17" s="16"/>
       <c r="AF17" s="16"/>
       <c r="AG17" s="16"/>
@@ -2107,82 +2626,80 @@
       <c r="AJ17" s="17"/>
       <c r="AK17" s="17"/>
       <c r="AL17" s="17">
-        <v>1.9087142857142859E-3</v>
+        <v>1.112266E-4</v>
       </c>
       <c r="AM17" s="17">
-        <v>4.0381428571428566E-6</v>
+        <v>3.8265572E-7</v>
       </c>
       <c r="AN17" s="17"/>
+      <c r="AO17" s="17"/>
+      <c r="AP17" s="17"/>
+      <c r="AQ17" s="17"/>
+      <c r="AR17" s="17"/>
+      <c r="AS17" s="17"/>
+      <c r="AT17" s="17"/>
+      <c r="AU17" s="17"/>
+      <c r="AV17" s="17"/>
+      <c r="AW17" s="17"/>
+      <c r="AX17" s="17"/>
+      <c r="AY17" s="17"/>
+      <c r="AZ17" s="17"/>
+      <c r="BA17" s="17"/>
+      <c r="BB17" s="17"/>
+      <c r="BC17" s="17"/>
+      <c r="BD17" s="17"/>
+      <c r="BE17" s="17"/>
+      <c r="BF17" s="17"/>
+      <c r="BG17" s="17"/>
+      <c r="BH17" s="17"/>
+      <c r="BI17" s="17"/>
+      <c r="BR17" s="26"/>
     </row>
-    <row r="18" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B18" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>37</v>
-      </c>
       <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="E18" s="16">
+        <v>1.7474571990000001</v>
+      </c>
       <c r="F18" s="16"/>
-      <c r="G18" s="16">
-        <v>0</v>
-      </c>
-      <c r="H18" s="16">
-        <v>0.70073684332157893</v>
-      </c>
-      <c r="I18" s="16">
-        <v>2.2484736842105271</v>
-      </c>
-      <c r="J18" s="16">
-        <v>0</v>
-      </c>
-      <c r="K18" s="16">
-        <v>1.7506639999999999E-5</v>
-      </c>
-      <c r="L18" s="16">
-        <v>7.2647368421052632E-7</v>
-      </c>
-      <c r="M18" s="16">
-        <v>6.5426315789473686E-9</v>
-      </c>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
       <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16">
-        <v>6.4736842105263159E-10</v>
-      </c>
-      <c r="R18" s="16">
-        <v>8.9642105263157898E-3</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.1239436842105263</v>
-      </c>
-      <c r="T18" s="16">
-        <v>1.3457894736842099E-2</v>
-      </c>
-      <c r="U18" s="16">
-        <v>2.1747368421052629E-10</v>
-      </c>
-      <c r="V18" s="16">
-        <v>0</v>
-      </c>
-      <c r="W18" s="16">
-        <v>4.7721052631578951E-9</v>
-      </c>
+      <c r="O18" s="16">
+        <v>8.5291107777777764E-2</v>
+      </c>
+      <c r="P18" s="16">
+        <v>4.2978444444444451E-3</v>
+      </c>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
       <c r="X18" s="16"/>
       <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
+      <c r="Z18" s="16">
+        <v>3.9874198888888886E-3</v>
+      </c>
       <c r="AA18" s="16"/>
       <c r="AB18" s="16"/>
-      <c r="AC18" s="16">
-        <v>1.226315789473684E-9</v>
-      </c>
-      <c r="AD18" s="16">
-        <v>4.3357894736842099E-7</v>
-      </c>
+      <c r="AC18" s="16"/>
+      <c r="AD18" s="16"/>
       <c r="AE18" s="16"/>
       <c r="AF18" s="16"/>
       <c r="AG18" s="16"/>
@@ -2191,238 +2708,4607 @@
       <c r="AJ18" s="17"/>
       <c r="AK18" s="17"/>
       <c r="AL18" s="17">
-        <v>6.9484210526315796E-5</v>
+        <v>5.318087777777778E-5</v>
       </c>
       <c r="AM18" s="17">
-        <v>8.9152631578947366E-8</v>
+        <v>1.2422499999999999E-7</v>
       </c>
       <c r="AN18" s="17"/>
+      <c r="AO18" s="17"/>
+      <c r="AP18" s="17"/>
+      <c r="AQ18" s="17"/>
+      <c r="AR18" s="17"/>
+      <c r="AS18" s="17"/>
+      <c r="AT18" s="17"/>
+      <c r="AU18" s="17"/>
+      <c r="AV18" s="17"/>
+      <c r="AW18" s="17"/>
+      <c r="AX18" s="17"/>
+      <c r="AY18" s="17"/>
+      <c r="AZ18" s="17"/>
+      <c r="BA18" s="17"/>
+      <c r="BB18" s="17"/>
+      <c r="BC18" s="17"/>
+      <c r="BD18" s="17"/>
+      <c r="BE18" s="17"/>
+      <c r="BF18" s="17"/>
+      <c r="BG18" s="17"/>
+      <c r="BH18" s="17"/>
+      <c r="BI18" s="17"/>
+      <c r="BR18" s="26"/>
     </row>
-    <row r="19" spans="1:40" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
+      <c r="E19" s="16">
+        <v>1.7058254113333331</v>
+      </c>
       <c r="F19" s="16"/>
-      <c r="G19" s="16">
-        <v>6.7541249999999997E-2</v>
-      </c>
-      <c r="H19" s="16">
-        <v>1.9175</v>
-      </c>
-      <c r="I19" s="16">
-        <v>8.8052999999999992E-2</v>
-      </c>
-      <c r="J19" s="16">
-        <v>1.4125E-7</v>
-      </c>
-      <c r="K19" s="16">
-        <v>1.7962500000000001E-9</v>
-      </c>
-      <c r="L19" s="16">
-        <v>0</v>
-      </c>
-      <c r="M19" s="16">
-        <v>0</v>
-      </c>
-      <c r="N19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16">
+        <v>3.2147823333333338E-3</v>
+      </c>
       <c r="O19" s="16"/>
       <c r="P19" s="16"/>
-      <c r="Q19" s="16">
-        <v>1.60125E-9</v>
-      </c>
-      <c r="R19" s="16">
-        <v>2.2487500000000001E-2</v>
-      </c>
-      <c r="S19" s="16">
-        <v>2.9510712499999999E-3</v>
-      </c>
-      <c r="T19" s="16">
-        <v>1.35E-2</v>
-      </c>
-      <c r="U19" s="16">
-        <v>1.5269475000000001E-6</v>
-      </c>
-      <c r="V19" s="16">
-        <v>1.0137499999999999E-9</v>
-      </c>
-      <c r="W19" s="16">
-        <v>0</v>
-      </c>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
       <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
+      <c r="Y19" s="16">
+        <v>5.5177503333333329E-2</v>
+      </c>
       <c r="Z19" s="16"/>
       <c r="AA19" s="16"/>
       <c r="AB19" s="16"/>
-      <c r="AC19" s="16">
-        <v>2.9012500000000001E-9</v>
-      </c>
-      <c r="AD19" s="16">
-        <v>0</v>
-      </c>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
       <c r="AE19" s="16"/>
-      <c r="AF19" s="16"/>
+      <c r="AF19" s="16">
+        <v>1.903965266666667E-2</v>
+      </c>
       <c r="AG19" s="16"/>
       <c r="AH19" s="17"/>
       <c r="AI19" s="17"/>
       <c r="AJ19" s="17"/>
-      <c r="AK19" s="17"/>
+      <c r="AK19" s="17">
+        <v>5.6988337333333333E-2</v>
+      </c>
       <c r="AL19" s="17">
-        <v>0</v>
+        <v>7.1930273333333334E-3</v>
       </c>
       <c r="AM19" s="17">
-        <v>0</v>
+        <v>4.2918900000000007E-5</v>
       </c>
       <c r="AN19" s="17"/>
+      <c r="AO19" s="17"/>
+      <c r="AP19" s="17"/>
+      <c r="AQ19" s="17"/>
+      <c r="AR19" s="24"/>
+      <c r="AS19" s="24"/>
+      <c r="AT19" s="24"/>
+      <c r="AU19" s="24"/>
+      <c r="AV19" s="24"/>
+      <c r="AW19" s="24"/>
+      <c r="AX19" s="24"/>
+      <c r="AY19" s="24"/>
+      <c r="AZ19" s="24"/>
+      <c r="BA19" s="24"/>
+      <c r="BB19" s="24"/>
+      <c r="BC19" s="24"/>
+      <c r="BD19" s="24"/>
+      <c r="BE19" s="24"/>
+      <c r="BF19" s="24"/>
+      <c r="BG19" s="24"/>
+      <c r="BH19" s="24"/>
+      <c r="BI19" s="24"/>
+      <c r="BR19" s="26"/>
     </row>
-    <row r="20" spans="1:40" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="21"/>
-      <c r="AC20" s="21"/>
-      <c r="AD20" s="21"/>
-      <c r="AE20" s="21"/>
-      <c r="AF20" s="21"/>
-      <c r="AG20" s="23"/>
+    <row r="20" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16">
+        <v>1.7058439592352941</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16">
+        <v>3.2147862352941178E-3</v>
+      </c>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16">
+        <v>5.5177408235294108E-2</v>
+      </c>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16">
+        <v>1.9039491882352939E-2</v>
+      </c>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="17"/>
+      <c r="AI20" s="17"/>
+      <c r="AJ20" s="17"/>
+      <c r="AK20" s="17">
+        <v>5.6988490352941179E-2</v>
+      </c>
+      <c r="AL20" s="17">
+        <v>7.9190535294117648E-4</v>
+      </c>
+      <c r="AM20" s="17">
+        <v>4.0952723529411756E-6</v>
+      </c>
+      <c r="AN20" s="17"/>
+      <c r="AO20" s="17"/>
+      <c r="AP20" s="17"/>
+      <c r="AQ20" s="17"/>
+      <c r="AR20" s="17"/>
+      <c r="AS20" s="17"/>
+      <c r="AT20" s="17"/>
+      <c r="AU20" s="17"/>
+      <c r="AV20" s="17"/>
+      <c r="AW20" s="17"/>
+      <c r="AX20" s="17"/>
+      <c r="AY20" s="17"/>
+      <c r="AZ20" s="17"/>
+      <c r="BA20" s="17"/>
+      <c r="BB20" s="17"/>
+      <c r="BC20" s="17"/>
+      <c r="BD20" s="17"/>
+      <c r="BE20" s="17"/>
+      <c r="BF20" s="17"/>
+      <c r="BG20" s="17"/>
+      <c r="BH20" s="17"/>
+      <c r="BI20" s="17"/>
+      <c r="BR20" s="26"/>
     </row>
-    <row r="21" spans="1:40" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="26"/>
-      <c r="AB21" s="21"/>
-      <c r="AC21" s="21"/>
-      <c r="AD21" s="21"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="21"/>
-      <c r="AG21" s="31"/>
+    <row r="21" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16">
+        <v>1.7058431281111111</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16">
+        <v>3.2147766111111109E-3</v>
+      </c>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16">
+        <v>5.5177409111111103E-2</v>
+      </c>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="16">
+        <v>1.903948744444444E-2</v>
+      </c>
+      <c r="AG21" s="16"/>
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="17"/>
+      <c r="AJ21" s="17"/>
+      <c r="AK21" s="17">
+        <v>5.6988436777777783E-2</v>
+      </c>
+      <c r="AL21" s="17">
+        <v>1.329076388888889E-4</v>
+      </c>
+      <c r="AM21" s="17">
+        <v>4.5402638888888879E-7</v>
+      </c>
+      <c r="AN21" s="17"/>
+      <c r="AO21" s="17"/>
+      <c r="AP21" s="17"/>
+      <c r="AQ21" s="17"/>
+      <c r="AR21" s="17"/>
+      <c r="AS21" s="17"/>
+      <c r="AT21" s="17"/>
+      <c r="AU21" s="17"/>
+      <c r="AV21" s="17"/>
+      <c r="AW21" s="17"/>
+      <c r="AX21" s="17"/>
+      <c r="AY21" s="17"/>
+      <c r="AZ21" s="17"/>
+      <c r="BA21" s="17"/>
+      <c r="BB21" s="17"/>
+      <c r="BC21" s="17"/>
+      <c r="BD21" s="17"/>
+      <c r="BE21" s="17"/>
+      <c r="BF21" s="17"/>
+      <c r="BG21" s="17"/>
+      <c r="BH21" s="17"/>
+      <c r="BI21" s="17"/>
+      <c r="BR21" s="26"/>
     </row>
-    <row r="22" spans="1:40" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="21"/>
-      <c r="AC22" s="21"/>
-      <c r="AD22" s="21"/>
-      <c r="AE22" s="21"/>
-      <c r="AF22" s="21"/>
-      <c r="AG22" s="28"/>
+    <row r="22" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16">
+        <v>1.705848962142857</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16">
+        <v>3.2147944285714279E-3</v>
+      </c>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16">
+        <v>5.5177084714285722E-2</v>
+      </c>
+      <c r="Z22" s="16"/>
+      <c r="AA22" s="16"/>
+      <c r="AB22" s="16"/>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16"/>
+      <c r="AE22" s="16"/>
+      <c r="AF22" s="16">
+        <v>1.903949928571428E-2</v>
+      </c>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="17"/>
+      <c r="AI22" s="17"/>
+      <c r="AJ22" s="17"/>
+      <c r="AK22" s="17">
+        <v>5.6988479428571437E-2</v>
+      </c>
+      <c r="AL22" s="17">
+        <v>1.5823754285714279E-4</v>
+      </c>
+      <c r="AM22" s="17">
+        <v>3.9447985714285712E-7</v>
+      </c>
+      <c r="AN22" s="17"/>
+      <c r="AO22" s="17"/>
+      <c r="AP22" s="17"/>
+      <c r="AQ22" s="17"/>
+      <c r="AR22" s="17"/>
+      <c r="AS22" s="17"/>
+      <c r="AT22" s="17"/>
+      <c r="AU22" s="17"/>
+      <c r="AV22" s="17"/>
+      <c r="AW22" s="17"/>
+      <c r="AX22" s="17"/>
+      <c r="AY22" s="17"/>
+      <c r="AZ22" s="17"/>
+      <c r="BA22" s="17"/>
+      <c r="BB22" s="17"/>
+      <c r="BC22" s="17"/>
+      <c r="BD22" s="17"/>
+      <c r="BE22" s="17"/>
+      <c r="BF22" s="17"/>
+      <c r="BG22" s="17"/>
+      <c r="BH22" s="17"/>
+      <c r="BI22" s="17"/>
+      <c r="BR22" s="26"/>
     </row>
-    <row r="23" spans="1:40" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="21"/>
-      <c r="W23" s="21"/>
-      <c r="X23" s="21"/>
-      <c r="Y23" s="21"/>
-      <c r="Z23" s="21"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="21"/>
-      <c r="AC23" s="21"/>
-      <c r="AD23" s="21"/>
-      <c r="AE23" s="21"/>
-      <c r="AF23" s="21"/>
-      <c r="AG23" s="28"/>
+    <row r="23" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16">
+        <v>1.705839675</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16">
+        <v>3.2147635E-3</v>
+      </c>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="16">
+        <v>5.5178027999999997E-2</v>
+      </c>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="16"/>
+      <c r="AB23" s="16"/>
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16"/>
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="16">
+        <v>1.9039469E-2</v>
+      </c>
+      <c r="AG23" s="16"/>
+      <c r="AH23" s="17"/>
+      <c r="AI23" s="17"/>
+      <c r="AJ23" s="17"/>
+      <c r="AK23" s="17">
+        <v>5.6988441500000001E-2</v>
+      </c>
+      <c r="AL23" s="17">
+        <v>7.2772800000000002E-5</v>
+      </c>
+      <c r="AM23" s="17">
+        <v>1.2615635000000001E-7</v>
+      </c>
+      <c r="AN23" s="17"/>
+      <c r="AO23" s="17"/>
+      <c r="AP23" s="17"/>
+      <c r="AQ23" s="17"/>
+      <c r="AR23" s="17"/>
+      <c r="AS23" s="17"/>
+      <c r="AT23" s="17"/>
+      <c r="AU23" s="17"/>
+      <c r="AV23" s="17"/>
+      <c r="AW23" s="17"/>
+      <c r="AX23" s="17"/>
+      <c r="AY23" s="17"/>
+      <c r="AZ23" s="17"/>
+      <c r="BA23" s="17"/>
+      <c r="BB23" s="17"/>
+      <c r="BC23" s="17"/>
+      <c r="BD23" s="17"/>
+      <c r="BE23" s="17"/>
+      <c r="BF23" s="17"/>
+      <c r="BG23" s="17"/>
+      <c r="BH23" s="17"/>
+      <c r="BI23" s="17"/>
+      <c r="BR23" s="26"/>
+    </row>
+    <row r="24" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16">
+        <v>1.1091141229999999</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16">
+        <v>1.4615107999999999E-3</v>
+      </c>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="16">
+        <v>3.3593184600000013E-2</v>
+      </c>
+      <c r="Z24" s="16"/>
+      <c r="AA24" s="16"/>
+      <c r="AB24" s="16"/>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="16"/>
+      <c r="AF24" s="16">
+        <v>1.14260218E-2</v>
+      </c>
+      <c r="AG24" s="16">
+        <v>0.56395642199999996</v>
+      </c>
+      <c r="AH24" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="17">
+        <v>2.6777834E-2</v>
+      </c>
+      <c r="AJ24" s="17"/>
+      <c r="AK24" s="17">
+        <v>3.5999945399999997E-2</v>
+      </c>
+      <c r="AL24" s="17">
+        <v>2.67050458E-2</v>
+      </c>
+      <c r="AM24" s="17">
+        <v>4.4454953999999999E-4</v>
+      </c>
+      <c r="AN24" s="17"/>
+      <c r="AO24" s="17"/>
+      <c r="AP24" s="17"/>
+      <c r="AQ24" s="17"/>
+      <c r="AR24" s="17"/>
+      <c r="AS24" s="17"/>
+      <c r="AT24" s="17"/>
+      <c r="AU24" s="17"/>
+      <c r="AV24" s="17"/>
+      <c r="AW24" s="17"/>
+      <c r="AX24" s="17"/>
+      <c r="AY24" s="17"/>
+      <c r="AZ24" s="17"/>
+      <c r="BA24" s="17"/>
+      <c r="BB24" s="17"/>
+      <c r="BC24" s="17"/>
+      <c r="BD24" s="17"/>
+      <c r="BE24" s="17"/>
+      <c r="BF24" s="17"/>
+      <c r="BG24" s="17"/>
+      <c r="BH24" s="17"/>
+      <c r="BI24" s="17"/>
+      <c r="BR24" s="26"/>
+    </row>
+    <row r="25" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16">
+        <v>1.1091178045000001</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16">
+        <v>1.461552625E-3</v>
+      </c>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
+      <c r="T25" s="16"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="16"/>
+      <c r="X25" s="16"/>
+      <c r="Y25" s="16">
+        <v>3.3592747375000002E-2</v>
+      </c>
+      <c r="Z25" s="16"/>
+      <c r="AA25" s="16"/>
+      <c r="AB25" s="16"/>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="16">
+        <v>1.1425976062500001E-2</v>
+      </c>
+      <c r="AG25" s="16">
+        <v>0.56395131249999997</v>
+      </c>
+      <c r="AH25" s="17">
+        <v>1.14246734375E-2</v>
+      </c>
+      <c r="AI25" s="17">
+        <v>1.5596421875E-2</v>
+      </c>
+      <c r="AJ25" s="17"/>
+      <c r="AK25" s="17">
+        <v>3.5999904625000002E-2</v>
+      </c>
+      <c r="AL25" s="17">
+        <v>1.6146733124999999E-3</v>
+      </c>
+      <c r="AM25" s="17">
+        <v>2.2330789999999999E-5</v>
+      </c>
+      <c r="AN25" s="17"/>
+      <c r="AO25" s="17"/>
+      <c r="AP25" s="17"/>
+      <c r="AQ25" s="17"/>
+      <c r="AR25" s="17"/>
+      <c r="AS25" s="17"/>
+      <c r="AT25" s="17"/>
+      <c r="AU25" s="17"/>
+      <c r="AV25" s="17"/>
+      <c r="AW25" s="17"/>
+      <c r="AX25" s="17"/>
+      <c r="AY25" s="17"/>
+      <c r="AZ25" s="17"/>
+      <c r="BA25" s="17"/>
+      <c r="BB25" s="17"/>
+      <c r="BC25" s="17"/>
+      <c r="BD25" s="17"/>
+      <c r="BE25" s="17"/>
+      <c r="BF25" s="17"/>
+      <c r="BG25" s="17"/>
+      <c r="BH25" s="17"/>
+      <c r="BI25" s="17"/>
+      <c r="BR25" s="26"/>
+    </row>
+    <row r="26" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16">
+        <v>1.109113873133333</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16">
+        <v>1.4615562E-3</v>
+      </c>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="16">
+        <v>3.3592821333333328E-2</v>
+      </c>
+      <c r="Z26" s="16"/>
+      <c r="AA26" s="16"/>
+      <c r="AB26" s="16"/>
+      <c r="AC26" s="16"/>
+      <c r="AD26" s="16"/>
+      <c r="AE26" s="16"/>
+      <c r="AF26" s="16">
+        <v>1.142605153333333E-2</v>
+      </c>
+      <c r="AG26" s="16">
+        <v>0.56395108459999999</v>
+      </c>
+      <c r="AH26" s="17">
+        <v>2.110228006666667E-2</v>
+      </c>
+      <c r="AI26" s="17">
+        <v>5.6754625333333341E-3</v>
+      </c>
+      <c r="AJ26" s="17"/>
+      <c r="AK26" s="17">
+        <v>3.6000157400000003E-2</v>
+      </c>
+      <c r="AL26" s="17">
+        <v>2.74166E-4</v>
+      </c>
+      <c r="AM26" s="17">
+        <v>2.6206906666666662E-6</v>
+      </c>
+      <c r="AN26" s="17"/>
+      <c r="AO26" s="17"/>
+      <c r="AP26" s="17"/>
+      <c r="AQ26" s="17"/>
+      <c r="AR26" s="17"/>
+      <c r="AS26" s="17"/>
+      <c r="AT26" s="17"/>
+      <c r="AU26" s="17"/>
+      <c r="AV26" s="17"/>
+      <c r="AW26" s="17"/>
+      <c r="AX26" s="17"/>
+      <c r="AY26" s="17"/>
+      <c r="AZ26" s="17"/>
+      <c r="BA26" s="17"/>
+      <c r="BB26" s="17"/>
+      <c r="BC26" s="17"/>
+      <c r="BD26" s="17"/>
+      <c r="BE26" s="17"/>
+      <c r="BF26" s="17"/>
+      <c r="BG26" s="17"/>
+      <c r="BH26" s="17"/>
+      <c r="BI26" s="17"/>
+      <c r="BR26" s="26"/>
+    </row>
+    <row r="27" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16">
+        <v>1.1091168203571431</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16">
+        <v>1.4615561428571429E-3</v>
+      </c>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="16">
+        <v>3.3593201928571431E-2</v>
+      </c>
+      <c r="Z27" s="16"/>
+      <c r="AA27" s="16"/>
+      <c r="AB27" s="16"/>
+      <c r="AC27" s="16"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="16">
+        <v>1.142599314285714E-2</v>
+      </c>
+      <c r="AG27" s="16">
+        <v>0.56395060885714288</v>
+      </c>
+      <c r="AH27" s="17">
+        <v>2.220479978571429E-2</v>
+      </c>
+      <c r="AI27" s="17">
+        <v>4.5732168571428564E-3</v>
+      </c>
+      <c r="AJ27" s="17"/>
+      <c r="AK27" s="17">
+        <v>3.5999876714285707E-2</v>
+      </c>
+      <c r="AL27" s="17">
+        <v>1.112760285714286E-4</v>
+      </c>
+      <c r="AM27" s="17">
+        <v>7.3929299999999997E-7</v>
+      </c>
+      <c r="AN27" s="17"/>
+      <c r="AO27" s="17"/>
+      <c r="AP27" s="17"/>
+      <c r="AQ27" s="17"/>
+      <c r="AR27" s="17"/>
+      <c r="AS27" s="17"/>
+      <c r="AT27" s="17"/>
+      <c r="AU27" s="17"/>
+      <c r="AV27" s="17"/>
+      <c r="AW27" s="17"/>
+      <c r="AX27" s="17"/>
+      <c r="AY27" s="17"/>
+      <c r="AZ27" s="17"/>
+      <c r="BA27" s="17"/>
+      <c r="BB27" s="17"/>
+      <c r="BC27" s="17"/>
+      <c r="BD27" s="17"/>
+      <c r="BE27" s="17"/>
+      <c r="BF27" s="17"/>
+      <c r="BG27" s="17"/>
+      <c r="BH27" s="17"/>
+      <c r="BI27" s="17"/>
+      <c r="BR27" s="26"/>
+    </row>
+    <row r="28" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16">
+        <v>0</v>
+      </c>
+      <c r="H28" s="16">
+        <v>0</v>
+      </c>
+      <c r="I28" s="16">
+        <v>3.350000000000001</v>
+      </c>
+      <c r="J28" s="16">
+        <v>0</v>
+      </c>
+      <c r="K28" s="16">
+        <v>1.2222857142857139E-4</v>
+      </c>
+      <c r="L28" s="16">
+        <v>3.107142857142857E-6</v>
+      </c>
+      <c r="M28" s="16">
+        <v>7.8757142857142862E-8</v>
+      </c>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16">
+        <v>0</v>
+      </c>
+      <c r="R28" s="16">
+        <v>0</v>
+      </c>
+      <c r="S28" s="16">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="T28" s="16">
+        <v>1.3342857142857141E-2</v>
+      </c>
+      <c r="U28" s="16">
+        <v>0</v>
+      </c>
+      <c r="V28" s="16">
+        <v>0</v>
+      </c>
+      <c r="W28" s="16">
+        <v>1.7242857142857141E-8</v>
+      </c>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="16"/>
+      <c r="Z28" s="16"/>
+      <c r="AA28" s="16"/>
+      <c r="AB28" s="16"/>
+      <c r="AC28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="16">
+        <v>3.0599999999999999E-6</v>
+      </c>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="17"/>
+      <c r="AI28" s="17"/>
+      <c r="AJ28" s="17"/>
+      <c r="AK28" s="17"/>
+      <c r="AL28" s="17">
+        <v>1.9087142857142859E-3</v>
+      </c>
+      <c r="AM28" s="17">
+        <v>4.0381428571428566E-6</v>
+      </c>
+      <c r="AN28" s="17"/>
+      <c r="AO28" s="17"/>
+      <c r="AP28" s="17"/>
+      <c r="AQ28" s="17"/>
+      <c r="AR28" s="17"/>
+      <c r="AS28" s="17"/>
+      <c r="AT28" s="17"/>
+      <c r="AU28" s="17"/>
+      <c r="AV28" s="17"/>
+      <c r="AW28" s="17"/>
+      <c r="AX28" s="17"/>
+      <c r="AY28" s="17"/>
+      <c r="AZ28" s="17"/>
+      <c r="BA28" s="17"/>
+      <c r="BB28" s="17"/>
+      <c r="BC28" s="17"/>
+      <c r="BD28" s="17"/>
+      <c r="BE28" s="17"/>
+      <c r="BF28" s="17"/>
+      <c r="BG28" s="17"/>
+      <c r="BH28" s="17"/>
+      <c r="BI28" s="17"/>
+      <c r="BR28" s="26"/>
+    </row>
+    <row r="29" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16">
+        <v>0</v>
+      </c>
+      <c r="H29" s="16">
+        <v>0.70073684332157893</v>
+      </c>
+      <c r="I29" s="16">
+        <v>2.2484736842105271</v>
+      </c>
+      <c r="J29" s="16">
+        <v>0</v>
+      </c>
+      <c r="K29" s="16">
+        <v>1.7506639999999999E-5</v>
+      </c>
+      <c r="L29" s="16">
+        <v>7.2647368421052632E-7</v>
+      </c>
+      <c r="M29" s="16">
+        <v>6.5426315789473686E-9</v>
+      </c>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16">
+        <v>6.4736842105263159E-10</v>
+      </c>
+      <c r="R29" s="16">
+        <v>8.9642105263157898E-3</v>
+      </c>
+      <c r="S29" s="16">
+        <v>0.1239436842105263</v>
+      </c>
+      <c r="T29" s="16">
+        <v>1.3457894736842099E-2</v>
+      </c>
+      <c r="U29" s="16">
+        <v>2.1747368421052629E-10</v>
+      </c>
+      <c r="V29" s="16">
+        <v>0</v>
+      </c>
+      <c r="W29" s="16">
+        <v>4.7721052631578951E-9</v>
+      </c>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+      <c r="AA29" s="16"/>
+      <c r="AB29" s="16"/>
+      <c r="AC29" s="16">
+        <v>1.226315789473684E-9</v>
+      </c>
+      <c r="AD29" s="16">
+        <v>4.3357894736842099E-7</v>
+      </c>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="17"/>
+      <c r="AI29" s="17"/>
+      <c r="AJ29" s="17"/>
+      <c r="AK29" s="17"/>
+      <c r="AL29" s="17">
+        <v>6.9484210526315796E-5</v>
+      </c>
+      <c r="AM29" s="17">
+        <v>8.9152631578947366E-8</v>
+      </c>
+      <c r="AN29" s="17"/>
+      <c r="AO29" s="17"/>
+      <c r="AP29" s="17"/>
+      <c r="AQ29" s="17"/>
+      <c r="AR29" s="17"/>
+      <c r="AS29" s="17"/>
+      <c r="AT29" s="17"/>
+      <c r="AU29" s="17"/>
+      <c r="AV29" s="17"/>
+      <c r="AW29" s="17"/>
+      <c r="AX29" s="17"/>
+      <c r="AY29" s="17"/>
+      <c r="AZ29" s="17"/>
+      <c r="BA29" s="17"/>
+      <c r="BB29" s="17"/>
+      <c r="BC29" s="17"/>
+      <c r="BD29" s="17"/>
+      <c r="BE29" s="17"/>
+      <c r="BF29" s="17"/>
+      <c r="BG29" s="17"/>
+      <c r="BH29" s="17"/>
+      <c r="BI29" s="17"/>
+      <c r="BR29" s="26"/>
+    </row>
+    <row r="30" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16">
+        <v>6.7541249999999997E-2</v>
+      </c>
+      <c r="H30" s="16">
+        <v>1.9175</v>
+      </c>
+      <c r="I30" s="16">
+        <v>8.8052999999999992E-2</v>
+      </c>
+      <c r="J30" s="16">
+        <v>1.4125E-7</v>
+      </c>
+      <c r="K30" s="16">
+        <v>1.7962500000000001E-9</v>
+      </c>
+      <c r="L30" s="16">
+        <v>0</v>
+      </c>
+      <c r="M30" s="16">
+        <v>0</v>
+      </c>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16">
+        <v>1.60125E-9</v>
+      </c>
+      <c r="R30" s="16">
+        <v>2.2487500000000001E-2</v>
+      </c>
+      <c r="S30" s="16">
+        <v>2.9510712499999999E-3</v>
+      </c>
+      <c r="T30" s="16">
+        <v>1.35E-2</v>
+      </c>
+      <c r="U30" s="16">
+        <v>1.5269475000000001E-6</v>
+      </c>
+      <c r="V30" s="16">
+        <v>1.0137499999999999E-9</v>
+      </c>
+      <c r="W30" s="16">
+        <v>0</v>
+      </c>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="16"/>
+      <c r="AA30" s="16"/>
+      <c r="AB30" s="16"/>
+      <c r="AC30" s="16">
+        <v>2.9012500000000001E-9</v>
+      </c>
+      <c r="AD30" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="16"/>
+      <c r="AF30" s="16"/>
+      <c r="AG30" s="16"/>
+      <c r="AH30" s="17"/>
+      <c r="AI30" s="17"/>
+      <c r="AJ30" s="17"/>
+      <c r="AK30" s="17"/>
+      <c r="AL30" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="17"/>
+      <c r="AO30" s="17"/>
+      <c r="AP30" s="17"/>
+      <c r="AQ30" s="17"/>
+      <c r="AR30" s="17"/>
+      <c r="AS30" s="17"/>
+      <c r="AT30" s="17"/>
+      <c r="AU30" s="17"/>
+      <c r="AV30" s="17"/>
+      <c r="AW30" s="17"/>
+      <c r="AX30" s="17"/>
+      <c r="AY30" s="17"/>
+      <c r="AZ30" s="17"/>
+      <c r="BA30" s="17"/>
+      <c r="BB30" s="17"/>
+      <c r="BC30" s="17"/>
+      <c r="BD30" s="17"/>
+      <c r="BE30" s="17"/>
+      <c r="BF30" s="17"/>
+      <c r="BG30" s="17"/>
+      <c r="BH30" s="17"/>
+      <c r="BI30" s="17"/>
+      <c r="BR30" s="26"/>
+    </row>
+    <row r="31" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16"/>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="16"/>
+      <c r="Z31" s="16"/>
+      <c r="AA31" s="16"/>
+      <c r="AB31" s="16"/>
+      <c r="AC31" s="16"/>
+      <c r="AD31" s="16"/>
+      <c r="AE31" s="16"/>
+      <c r="AF31" s="16"/>
+      <c r="AG31" s="16"/>
+      <c r="AH31" s="17"/>
+      <c r="AI31" s="17"/>
+      <c r="AJ31" s="17"/>
+      <c r="AK31" s="17"/>
+      <c r="AL31" s="17"/>
+      <c r="AM31" s="17"/>
+      <c r="AN31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR31" s="17">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="AS31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT31" s="17">
+        <v>0.17500000000000002</v>
+      </c>
+      <c r="AU31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AW31" s="17">
+        <v>0.67147499999999993</v>
+      </c>
+      <c r="AX31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY31" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ31" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA31" s="17">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="BB31" s="17">
+        <v>0.01</v>
+      </c>
+      <c r="BC31" s="17">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="BD31" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE31" s="17">
+        <v>0.115</v>
+      </c>
+      <c r="BF31" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG31" s="17">
+        <v>2.2499999999999999E-4</v>
+      </c>
+      <c r="BH31" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="17">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="BJ31">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BK31">
+        <v>0</v>
+      </c>
+      <c r="BL31">
+        <v>0</v>
+      </c>
+      <c r="BM31">
+        <v>0</v>
+      </c>
+      <c r="BN31">
+        <v>0</v>
+      </c>
+      <c r="BO31">
+        <v>0</v>
+      </c>
+      <c r="BP31">
+        <v>0</v>
+      </c>
+      <c r="BQ31">
+        <v>0</v>
+      </c>
+      <c r="BR31" s="26"/>
+    </row>
+    <row r="32" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="16"/>
+      <c r="Z32" s="16"/>
+      <c r="AA32" s="16"/>
+      <c r="AB32" s="16"/>
+      <c r="AC32" s="16"/>
+      <c r="AD32" s="16"/>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="16"/>
+      <c r="AG32" s="16"/>
+      <c r="AH32" s="17"/>
+      <c r="AI32" s="17"/>
+      <c r="AJ32" s="17"/>
+      <c r="AK32" s="17"/>
+      <c r="AL32" s="17"/>
+      <c r="AM32" s="17"/>
+      <c r="AN32" s="17">
+        <v>0.93495000000000006</v>
+      </c>
+      <c r="AO32" s="17">
+        <v>4.2500000000000003E-3</v>
+      </c>
+      <c r="AP32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AU32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="17">
+        <v>0.04</v>
+      </c>
+      <c r="AW32" s="17">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="AX32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY32" s="17">
+        <v>0.01</v>
+      </c>
+      <c r="AZ32" s="17">
+        <v>5.2500000000000003E-3</v>
+      </c>
+      <c r="BA32" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB32" s="17">
+        <v>1.25E-3</v>
+      </c>
+      <c r="BC32" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD32" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE32" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF32" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG32" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH32" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="BK32">
+        <v>0</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="BQ32">
+        <v>1.25E-3</v>
+      </c>
+      <c r="BR32" s="26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
+      <c r="X33" s="16"/>
+      <c r="Y33" s="16"/>
+      <c r="Z33" s="16"/>
+      <c r="AA33" s="16"/>
+      <c r="AB33" s="16"/>
+      <c r="AC33" s="16"/>
+      <c r="AD33" s="16"/>
+      <c r="AE33" s="16"/>
+      <c r="AF33" s="16"/>
+      <c r="AG33" s="16"/>
+      <c r="AH33" s="17"/>
+      <c r="AI33" s="17"/>
+      <c r="AJ33" s="17"/>
+      <c r="AK33" s="17"/>
+      <c r="AL33" s="17"/>
+      <c r="AM33" s="17"/>
+      <c r="AN33" s="17">
+        <v>0.94374999999999998</v>
+      </c>
+      <c r="AO33" s="17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AP33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT33" s="17">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="AU33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV33" s="17">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="AW33" s="17">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AX33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY33" s="17">
+        <v>9.5000000000000015E-3</v>
+      </c>
+      <c r="AZ33" s="17">
+        <v>5.2500000000000003E-3</v>
+      </c>
+      <c r="BA33" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB33" s="17">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="BC33" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD33" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE33" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF33" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG33" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH33" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI33" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ33">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="BK33">
+        <v>0</v>
+      </c>
+      <c r="BL33">
+        <v>0</v>
+      </c>
+      <c r="BM33">
+        <v>0</v>
+      </c>
+      <c r="BN33">
+        <v>0</v>
+      </c>
+      <c r="BO33">
+        <v>0</v>
+      </c>
+      <c r="BP33">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="BQ33">
+        <v>1.7499999999999998E-3</v>
+      </c>
+      <c r="BR33" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16"/>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AE34" s="16"/>
+      <c r="AF34" s="16"/>
+      <c r="AG34" s="16"/>
+      <c r="AH34" s="17"/>
+      <c r="AI34" s="17"/>
+      <c r="AJ34" s="17"/>
+      <c r="AK34" s="17"/>
+      <c r="AL34" s="17"/>
+      <c r="AM34" s="17"/>
+      <c r="AN34" s="17">
+        <v>0.92754999999999999</v>
+      </c>
+      <c r="AO34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="17">
+        <v>6.3E-2</v>
+      </c>
+      <c r="AW34" s="17">
+        <v>1.5E-3</v>
+      </c>
+      <c r="AX34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ34" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="BA34" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB34" s="17">
+        <v>3.0000000000000005E-3</v>
+      </c>
+      <c r="BC34" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD34" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE34" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF34" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG34" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH34" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI34" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ34">
+        <v>1E-3</v>
+      </c>
+      <c r="BK34">
+        <v>0</v>
+      </c>
+      <c r="BL34">
+        <v>0</v>
+      </c>
+      <c r="BM34">
+        <v>6.0000000000000006E-4</v>
+      </c>
+      <c r="BN34">
+        <v>1E-3</v>
+      </c>
+      <c r="BO34">
+        <v>0</v>
+      </c>
+      <c r="BP34">
+        <v>1.7499999999999998E-3</v>
+      </c>
+      <c r="BQ34">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="BR34" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
+      <c r="S35" s="16"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="16"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
+      <c r="X35" s="16"/>
+      <c r="Y35" s="16"/>
+      <c r="Z35" s="16"/>
+      <c r="AA35" s="16"/>
+      <c r="AB35" s="16"/>
+      <c r="AC35" s="16"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="17"/>
+      <c r="AI35" s="17"/>
+      <c r="AJ35" s="17"/>
+      <c r="AK35" s="17"/>
+      <c r="AL35" s="17"/>
+      <c r="AM35" s="17"/>
+      <c r="AN35" s="17">
+        <v>0.9425</v>
+      </c>
+      <c r="AO35" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP35" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR35" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS35" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT35" s="17">
+        <v>1.25E-3</v>
+      </c>
+      <c r="AU35" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV35" s="17">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AW35" s="17">
+        <v>2E-3</v>
+      </c>
+      <c r="AX35" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY35" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ35" s="17">
+        <v>5.0499999999999996E-2</v>
+      </c>
+      <c r="BA35" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB35" s="17">
+        <v>1.25E-3</v>
+      </c>
+      <c r="BC35" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD35" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE35" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF35" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG35" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH35" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI35" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ35">
+        <v>1.5E-3</v>
+      </c>
+      <c r="BK35">
+        <v>0</v>
+      </c>
+      <c r="BL35">
+        <v>0</v>
+      </c>
+      <c r="BM35">
+        <v>0</v>
+      </c>
+      <c r="BN35">
+        <v>0</v>
+      </c>
+      <c r="BO35">
+        <v>0</v>
+      </c>
+      <c r="BP35">
+        <v>0</v>
+      </c>
+      <c r="BQ35">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="BR35" s="26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16"/>
+      <c r="Y36" s="16"/>
+      <c r="Z36" s="16"/>
+      <c r="AA36" s="16"/>
+      <c r="AB36" s="16"/>
+      <c r="AC36" s="16"/>
+      <c r="AD36" s="16"/>
+      <c r="AE36" s="16"/>
+      <c r="AF36" s="16"/>
+      <c r="AG36" s="16"/>
+      <c r="AH36" s="17"/>
+      <c r="AI36" s="17"/>
+      <c r="AJ36" s="17"/>
+      <c r="AK36" s="17"/>
+      <c r="AL36" s="17"/>
+      <c r="AM36" s="17"/>
+      <c r="AN36" s="17">
+        <v>0.97305000000000008</v>
+      </c>
+      <c r="AO36" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP36" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR36" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS36" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT36" s="17">
+        <v>1.9499999999999999E-3</v>
+      </c>
+      <c r="AU36" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV36" s="17">
+        <v>2.7500000000000003E-3</v>
+      </c>
+      <c r="AW36" s="17">
+        <v>3.4999999999999996E-3</v>
+      </c>
+      <c r="AX36" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY36" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ36" s="17">
+        <v>0.01</v>
+      </c>
+      <c r="BA36" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB36" s="17">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="BC36" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD36" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE36" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF36" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG36" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH36" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ36">
+        <v>6.000000000000001E-3</v>
+      </c>
+      <c r="BK36">
+        <v>0</v>
+      </c>
+      <c r="BL36">
+        <v>0</v>
+      </c>
+      <c r="BM36">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="BN36">
+        <v>0</v>
+      </c>
+      <c r="BO36">
+        <v>0</v>
+      </c>
+      <c r="BP36">
+        <v>0</v>
+      </c>
+      <c r="BQ36">
+        <v>1.25E-3</v>
+      </c>
+      <c r="BR36" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="16"/>
+      <c r="Z37" s="16"/>
+      <c r="AA37" s="16"/>
+      <c r="AB37" s="16"/>
+      <c r="AC37" s="16"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="17"/>
+      <c r="AI37" s="17"/>
+      <c r="AJ37" s="17"/>
+      <c r="AK37" s="17"/>
+      <c r="AL37" s="17"/>
+      <c r="AM37" s="17"/>
+      <c r="AN37" s="17">
+        <v>0.89370000000000005</v>
+      </c>
+      <c r="AO37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT37" s="17">
+        <v>2.3E-3</v>
+      </c>
+      <c r="AU37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV37" s="17">
+        <v>1.6E-2</v>
+      </c>
+      <c r="AW37" s="17">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AX37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY37" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ37" s="17">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="BA37" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB37" s="17">
+        <v>1.5E-3</v>
+      </c>
+      <c r="BC37" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD37" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE37" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF37" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG37" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH37" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI37" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>2E-3</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>1E-3</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>0</v>
+      </c>
+      <c r="BQ37">
+        <v>5.5999999999999994E-2</v>
+      </c>
+      <c r="BR37" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="16"/>
+      <c r="V38" s="16"/>
+      <c r="W38" s="16"/>
+      <c r="X38" s="16"/>
+      <c r="Y38" s="16"/>
+      <c r="Z38" s="16"/>
+      <c r="AA38" s="16"/>
+      <c r="AB38" s="16"/>
+      <c r="AC38" s="16"/>
+      <c r="AD38" s="16"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="16"/>
+      <c r="AG38" s="16"/>
+      <c r="AH38" s="17"/>
+      <c r="AI38" s="17"/>
+      <c r="AJ38" s="17"/>
+      <c r="AK38" s="17"/>
+      <c r="AL38" s="17"/>
+      <c r="AM38" s="17"/>
+      <c r="AN38" s="17">
+        <v>0.18850000000000003</v>
+      </c>
+      <c r="AO38" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR38" s="17">
+        <v>0.71188474221739839</v>
+      </c>
+      <c r="AS38" s="17">
+        <v>1.4952171334431635E-2</v>
+      </c>
+      <c r="AT38" s="17">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="AU38" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV38" s="17">
+        <v>1.0000000000000002E-4</v>
+      </c>
+      <c r="AW38" s="17">
+        <v>4.0000000000000007E-4</v>
+      </c>
+      <c r="AX38" s="17">
+        <v>2.5194412778215047E-2</v>
+      </c>
+      <c r="AY38" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ38" s="17">
+        <v>1.01E-2</v>
+      </c>
+      <c r="BA38" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB38" s="17">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="BC38" s="17">
+        <v>2.3733650748451275E-2</v>
+      </c>
+      <c r="BD38" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE38" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF38" s="17">
+        <v>2.4235022921503618E-2</v>
+      </c>
+      <c r="BG38" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH38" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI38" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ38">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="BK38">
+        <v>0</v>
+      </c>
+      <c r="BL38">
+        <v>0</v>
+      </c>
+      <c r="BM38">
+        <v>0</v>
+      </c>
+      <c r="BN38">
+        <v>0</v>
+      </c>
+      <c r="BO38">
+        <v>0</v>
+      </c>
+      <c r="BP38">
+        <v>0</v>
+      </c>
+      <c r="BQ38">
+        <v>1.0000000000000002E-4</v>
+      </c>
+      <c r="BR38" s="26"/>
+    </row>
+    <row r="39" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="16"/>
+      <c r="R39" s="16"/>
+      <c r="S39" s="16"/>
+      <c r="T39" s="16"/>
+      <c r="U39" s="16"/>
+      <c r="V39" s="16"/>
+      <c r="W39" s="16"/>
+      <c r="X39" s="16"/>
+      <c r="Y39" s="16"/>
+      <c r="Z39" s="16"/>
+      <c r="AA39" s="16"/>
+      <c r="AB39" s="16"/>
+      <c r="AC39" s="16"/>
+      <c r="AD39" s="16"/>
+      <c r="AE39" s="16"/>
+      <c r="AF39" s="16"/>
+      <c r="AG39" s="16"/>
+      <c r="AH39" s="17"/>
+      <c r="AI39" s="17"/>
+      <c r="AJ39" s="17"/>
+      <c r="AK39" s="17"/>
+      <c r="AL39" s="17"/>
+      <c r="AM39" s="17"/>
+      <c r="AN39" s="17">
+        <v>0.87178107420034889</v>
+      </c>
+      <c r="AO39" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR39" s="17">
+        <v>1.3046301597026464E-5</v>
+      </c>
+      <c r="AS39" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT39" s="17">
+        <v>2.1188194375496208E-3</v>
+      </c>
+      <c r="AU39" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV39" s="17">
+        <v>1.5124266841894017E-2</v>
+      </c>
+      <c r="AW39" s="17">
+        <v>1.1226360879527226E-3</v>
+      </c>
+      <c r="AX39" s="17">
+        <v>2.4461815494424619E-6</v>
+      </c>
+      <c r="AY39" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="17">
+        <v>2.2415200679061231E-2</v>
+      </c>
+      <c r="BA39" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB39" s="17">
+        <v>6.0176174287133305E-4</v>
+      </c>
+      <c r="BC39" s="17">
+        <v>8.1539384981415406E-6</v>
+      </c>
+      <c r="BD39" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE39" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF39" s="17">
+        <v>3.2615753992566162E-5</v>
+      </c>
+      <c r="BG39" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH39" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI39" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ39">
+        <v>8.731252093400957E-4</v>
+      </c>
+      <c r="BK39">
+        <v>0</v>
+      </c>
+      <c r="BL39">
+        <v>0</v>
+      </c>
+      <c r="BM39">
+        <v>2.9720943500776056E-2</v>
+      </c>
+      <c r="BN39">
+        <v>1.3046301597026463E-3</v>
+      </c>
+      <c r="BO39">
+        <v>0</v>
+      </c>
+      <c r="BP39">
+        <v>0</v>
+      </c>
+      <c r="BQ39">
+        <v>5.4881279964866143E-2</v>
+      </c>
+      <c r="BR39" s="26"/>
+    </row>
+    <row r="40" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16"/>
+      <c r="S40" s="16"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="16"/>
+      <c r="V40" s="16"/>
+      <c r="W40" s="16"/>
+      <c r="X40" s="16"/>
+      <c r="Y40" s="16"/>
+      <c r="Z40" s="16"/>
+      <c r="AA40" s="16"/>
+      <c r="AB40" s="16"/>
+      <c r="AC40" s="16"/>
+      <c r="AD40" s="16"/>
+      <c r="AE40" s="16"/>
+      <c r="AF40" s="16"/>
+      <c r="AG40" s="16"/>
+      <c r="AH40" s="17"/>
+      <c r="AI40" s="17"/>
+      <c r="AJ40" s="17"/>
+      <c r="AK40" s="17"/>
+      <c r="AL40" s="17"/>
+      <c r="AM40" s="17"/>
+      <c r="AN40" s="17">
+        <v>0.71496000000000015</v>
+      </c>
+      <c r="AO40" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP40" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ40" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR40" s="17">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="AS40" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT40" s="17">
+        <v>3.6840000000000005E-2</v>
+      </c>
+      <c r="AU40" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV40" s="17">
+        <v>1.2800000000000002E-2</v>
+      </c>
+      <c r="AW40" s="17">
+        <v>0.136295</v>
+      </c>
+      <c r="AX40" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY40" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="17">
+        <v>0.02</v>
+      </c>
+      <c r="BA40" s="17">
+        <v>4.5000000000000005E-3</v>
+      </c>
+      <c r="BB40" s="17">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="BC40" s="17">
+        <v>1.0000000000000002E-4</v>
+      </c>
+      <c r="BD40" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE40" s="17">
+        <v>2.3000000000000003E-2</v>
+      </c>
+      <c r="BF40" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG40" s="17">
+        <v>4.4999999999999996E-5</v>
+      </c>
+      <c r="BH40" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI40" s="17">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="BJ40">
+        <v>2.6000000000000003E-3</v>
+      </c>
+      <c r="BK40">
+        <v>0</v>
+      </c>
+      <c r="BL40">
+        <v>0</v>
+      </c>
+      <c r="BM40">
+        <v>8.0000000000000015E-4</v>
+      </c>
+      <c r="BN40">
+        <v>0</v>
+      </c>
+      <c r="BO40">
+        <v>0</v>
+      </c>
+      <c r="BP40">
+        <v>0</v>
+      </c>
+      <c r="BQ40">
+        <v>4.48E-2</v>
+      </c>
+      <c r="BR40" s="26"/>
+    </row>
+    <row r="41" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="16"/>
+      <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16"/>
+      <c r="S41" s="16"/>
+      <c r="T41" s="16"/>
+      <c r="U41" s="16"/>
+      <c r="V41" s="16"/>
+      <c r="W41" s="16"/>
+      <c r="X41" s="16"/>
+      <c r="Y41" s="16"/>
+      <c r="Z41" s="16"/>
+      <c r="AA41" s="16"/>
+      <c r="AB41" s="16"/>
+      <c r="AC41" s="16"/>
+      <c r="AD41" s="16"/>
+      <c r="AE41" s="16"/>
+      <c r="AF41" s="16"/>
+      <c r="AG41" s="16"/>
+      <c r="AH41" s="17"/>
+      <c r="AI41" s="17"/>
+      <c r="AJ41" s="17"/>
+      <c r="AK41" s="17"/>
+      <c r="AL41" s="17"/>
+      <c r="AM41" s="17"/>
+      <c r="AN41" s="17">
+        <v>0.93159295655076491</v>
+      </c>
+      <c r="AO41" s="17">
+        <v>2.3219682892906815E-3</v>
+      </c>
+      <c r="AP41" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ41" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR41" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS41" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT41" s="17">
+        <v>0</v>
+      </c>
+      <c r="AU41" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV41" s="17">
+        <v>5.0434053963838661E-2</v>
+      </c>
+      <c r="AW41" s="17">
+        <v>1.0902408901251738E-3</v>
+      </c>
+      <c r="AX41" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY41" s="17">
+        <v>5.4634547983310154E-3</v>
+      </c>
+      <c r="AZ41" s="17">
+        <v>2.9136792211404729E-3</v>
+      </c>
+      <c r="BA41" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB41" s="17">
+        <v>2.0438954102920725E-3</v>
+      </c>
+      <c r="BC41" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD41" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE41" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF41" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG41" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH41" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI41" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ41">
+        <v>7.8146180806675934E-4</v>
+      </c>
+      <c r="BK41">
+        <v>0</v>
+      </c>
+      <c r="BL41">
+        <v>0</v>
+      </c>
+      <c r="BM41">
+        <v>5.4536545201668994E-4</v>
+      </c>
+      <c r="BN41">
+        <v>4.5365452016689844E-4</v>
+      </c>
+      <c r="BO41">
+        <v>0</v>
+      </c>
+      <c r="BP41">
+        <v>1.4495099860917942E-3</v>
+      </c>
+      <c r="BQ41">
+        <v>9.0975910987482614E-4</v>
+      </c>
+      <c r="BR41" s="26"/>
+    </row>
+    <row r="42" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16"/>
+      <c r="Q42" s="16"/>
+      <c r="R42" s="16"/>
+      <c r="S42" s="16"/>
+      <c r="T42" s="16"/>
+      <c r="U42" s="16"/>
+      <c r="V42" s="16"/>
+      <c r="W42" s="16"/>
+      <c r="X42" s="16"/>
+      <c r="Y42" s="16"/>
+      <c r="Z42" s="16"/>
+      <c r="AA42" s="16"/>
+      <c r="AB42" s="16"/>
+      <c r="AC42" s="16"/>
+      <c r="AD42" s="16"/>
+      <c r="AE42" s="16"/>
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="17"/>
+      <c r="AI42" s="17"/>
+      <c r="AJ42" s="17"/>
+      <c r="AK42" s="17"/>
+      <c r="AL42" s="17"/>
+      <c r="AM42" s="17"/>
+      <c r="AN42" s="17">
+        <v>0.91773276567078987</v>
+      </c>
+      <c r="AO42" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR42" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS42" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT42" s="17">
+        <v>6.670498953377735E-4</v>
+      </c>
+      <c r="AU42" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV42" s="17">
+        <v>4.9368980399619407E-2</v>
+      </c>
+      <c r="AW42" s="17">
+        <v>1.7900216936251191E-3</v>
+      </c>
+      <c r="AX42" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY42" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="17">
+        <v>7.3215401712654607E-3</v>
+      </c>
+      <c r="BA42" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB42" s="17">
+        <v>2.5649674595623218E-3</v>
+      </c>
+      <c r="BC42" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD42" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE42" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF42" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG42" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH42" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ42">
+        <v>1.2900216936251191E-3</v>
+      </c>
+      <c r="BK42">
+        <v>0</v>
+      </c>
+      <c r="BL42">
+        <v>0</v>
+      </c>
+      <c r="BM42">
+        <v>7.1600867745004763E-4</v>
+      </c>
+      <c r="BN42">
+        <v>7.0997830637488119E-4</v>
+      </c>
+      <c r="BO42">
+        <v>0</v>
+      </c>
+      <c r="BP42">
+        <v>1.2424620361560419E-3</v>
+      </c>
+      <c r="BQ42">
+        <v>1.6596203996194096E-2</v>
+      </c>
+      <c r="BR42" s="26"/>
+    </row>
+    <row r="43" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="16"/>
+      <c r="O43" s="16"/>
+      <c r="P43" s="16"/>
+      <c r="Q43" s="16"/>
+      <c r="R43" s="16"/>
+      <c r="S43" s="16"/>
+      <c r="T43" s="16"/>
+      <c r="U43" s="16"/>
+      <c r="V43" s="16"/>
+      <c r="W43" s="16"/>
+      <c r="X43" s="16"/>
+      <c r="Y43" s="16"/>
+      <c r="Z43" s="16"/>
+      <c r="AA43" s="16"/>
+      <c r="AB43" s="16"/>
+      <c r="AC43" s="16"/>
+      <c r="AD43" s="16"/>
+      <c r="AE43" s="16"/>
+      <c r="AF43" s="16"/>
+      <c r="AG43" s="16"/>
+      <c r="AH43" s="17"/>
+      <c r="AI43" s="17"/>
+      <c r="AJ43" s="17"/>
+      <c r="AK43" s="17"/>
+      <c r="AL43" s="17"/>
+      <c r="AM43" s="17"/>
+      <c r="AN43" s="17">
+        <v>0.30475817181229514</v>
+      </c>
+      <c r="AO43" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP43" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR43" s="17">
+        <v>2.8699924984246179E-4</v>
+      </c>
+      <c r="AS43" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT43" s="17">
+        <v>3.8261094810747916E-4</v>
+      </c>
+      <c r="AU43" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV43" s="17">
+        <v>3.5339923152271856E-3</v>
+      </c>
+      <c r="AW43" s="17">
+        <v>1.6059030059215103E-3</v>
+      </c>
+      <c r="AX43" s="17">
+        <v>5.3812359345461582E-5</v>
+      </c>
+      <c r="AY43" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ43" s="17">
+        <v>5.4697434418686155E-3</v>
+      </c>
+      <c r="BA43" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB43" s="17">
+        <v>2.1526449228158039E-4</v>
+      </c>
+      <c r="BC43" s="17">
+        <v>1.7937453115153863E-4</v>
+      </c>
+      <c r="BD43" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE43" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF43" s="17">
+        <v>7.174981246061545E-4</v>
+      </c>
+      <c r="BG43" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH43" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI43" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ43">
+        <v>7.4796959520101816E-4</v>
+      </c>
+      <c r="BK43">
+        <v>0</v>
+      </c>
+      <c r="BL43">
+        <v>0</v>
+      </c>
+      <c r="BM43">
+        <v>0.64358630977045383</v>
+      </c>
+      <c r="BN43">
+        <v>2.8699924984246179E-2</v>
+      </c>
+      <c r="BO43">
+        <v>0</v>
+      </c>
+      <c r="BP43">
+        <v>1.1650657381557769E-4</v>
+      </c>
+      <c r="BQ43">
+        <v>9.6459187956363778E-3</v>
+      </c>
+      <c r="BR43" s="26"/>
+    </row>
+    <row r="44" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="16"/>
+      <c r="Q44" s="16"/>
+      <c r="R44" s="16"/>
+      <c r="S44" s="16"/>
+      <c r="T44" s="16"/>
+      <c r="U44" s="16"/>
+      <c r="V44" s="16"/>
+      <c r="W44" s="16"/>
+      <c r="X44" s="16"/>
+      <c r="Y44" s="16"/>
+      <c r="Z44" s="16"/>
+      <c r="AA44" s="16"/>
+      <c r="AB44" s="16"/>
+      <c r="AC44" s="16"/>
+      <c r="AD44" s="16"/>
+      <c r="AE44" s="16"/>
+      <c r="AF44" s="16"/>
+      <c r="AG44" s="16"/>
+      <c r="AH44" s="17"/>
+      <c r="AI44" s="17"/>
+      <c r="AJ44" s="17"/>
+      <c r="AK44" s="17"/>
+      <c r="AL44" s="17"/>
+      <c r="AM44" s="17"/>
+      <c r="AN44" s="17">
+        <v>4.0823452147772535E-3</v>
+      </c>
+      <c r="AO44" s="17">
+        <v>2.0535512351211673E-2</v>
+      </c>
+      <c r="AP44" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="17">
+        <v>2.6363109750369198E-5</v>
+      </c>
+      <c r="AR44" s="17">
+        <v>4.0081937612832728E-4</v>
+      </c>
+      <c r="AS44" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT44" s="17">
+        <v>0.18111368949071971</v>
+      </c>
+      <c r="AU44" s="17">
+        <v>5.0168644456300912E-3</v>
+      </c>
+      <c r="AV44" s="17">
+        <v>1.3453167142130256E-2</v>
+      </c>
+      <c r="AW44" s="17">
+        <v>0.21739826177399543</v>
+      </c>
+      <c r="AX44" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY44" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA44" s="17">
+        <v>3.265411003637602E-2</v>
+      </c>
+      <c r="BB44" s="17">
+        <v>2.6987140494578333E-3</v>
+      </c>
+      <c r="BC44" s="17">
+        <v>4.8075093905217908E-5</v>
+      </c>
+      <c r="BD44" s="17">
+        <v>3.9928274028218531E-2</v>
+      </c>
+      <c r="BE44" s="17">
+        <v>0.45516869099734919</v>
+      </c>
+      <c r="BF44" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG44" s="17">
+        <v>9.5017720480093746E-5</v>
+      </c>
+      <c r="BH44" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI44" s="17">
+        <v>8.4068379470899712E-5</v>
+      </c>
+      <c r="BJ44">
+        <v>2.2179631104056541E-3</v>
+      </c>
+      <c r="BK44">
+        <v>0</v>
+      </c>
+      <c r="BL44">
+        <v>1.9477206843033433E-4</v>
+      </c>
+      <c r="BM44">
+        <v>7.0678656173432039E-3</v>
+      </c>
+      <c r="BN44">
+        <v>0</v>
+      </c>
+      <c r="BO44">
+        <v>4.4856923080936219E-4</v>
+      </c>
+      <c r="BP44">
+        <v>1.7366856763410658E-2</v>
+      </c>
+      <c r="BQ44">
+        <v>0</v>
+      </c>
+      <c r="BR44" s="26"/>
+    </row>
+    <row r="45" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="16"/>
+      <c r="AB45" s="16"/>
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="16"/>
+      <c r="AF45" s="16"/>
+      <c r="AG45" s="16"/>
+      <c r="AH45" s="17"/>
+      <c r="AI45" s="17"/>
+      <c r="AJ45" s="17"/>
+      <c r="AK45" s="17"/>
+      <c r="AL45" s="17"/>
+      <c r="AM45" s="17"/>
+      <c r="AN45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR45" s="17">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="AS45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="17">
+        <v>0.17500000000000002</v>
+      </c>
+      <c r="AU45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AW45" s="17">
+        <v>0.67147499999999993</v>
+      </c>
+      <c r="AX45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY45" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ45" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA45" s="17">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="BB45" s="17">
+        <v>0.01</v>
+      </c>
+      <c r="BC45" s="17">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="BD45" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE45" s="17">
+        <v>0.115</v>
+      </c>
+      <c r="BF45" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG45" s="17">
+        <v>2.2499999999999999E-4</v>
+      </c>
+      <c r="BH45" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI45" s="17">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="BJ45">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BK45">
+        <v>0</v>
+      </c>
+      <c r="BL45">
+        <v>0</v>
+      </c>
+      <c r="BM45">
+        <v>0</v>
+      </c>
+      <c r="BN45">
+        <v>0</v>
+      </c>
+      <c r="BO45">
+        <v>0</v>
+      </c>
+      <c r="BP45">
+        <v>0</v>
+      </c>
+      <c r="BQ45">
+        <v>0</v>
+      </c>
+      <c r="BR45" s="26"/>
+    </row>
+    <row r="46" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
+      <c r="Z46" s="16"/>
+      <c r="AA46" s="16"/>
+      <c r="AB46" s="16"/>
+      <c r="AC46" s="16"/>
+      <c r="AD46" s="16"/>
+      <c r="AE46" s="16"/>
+      <c r="AF46" s="16"/>
+      <c r="AG46" s="16"/>
+      <c r="AH46" s="17"/>
+      <c r="AI46" s="17"/>
+      <c r="AJ46" s="17"/>
+      <c r="AK46" s="17"/>
+      <c r="AL46" s="17"/>
+      <c r="AM46" s="17"/>
+      <c r="AN46" s="17">
+        <v>0.31011</v>
+      </c>
+      <c r="AO46" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR46" s="17">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="AS46" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="17">
+        <v>6.9000000000000008E-4</v>
+      </c>
+      <c r="AU46" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="17">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="AW46" s="17">
+        <v>1.8E-3</v>
+      </c>
+      <c r="AX46" s="17">
+        <v>5.2499999999999995E-5</v>
+      </c>
+      <c r="AY46" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="17">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="BA46" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="17">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="BC46" s="17">
+        <v>1.75E-4</v>
+      </c>
+      <c r="BD46" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE46" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF46" s="17">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="BG46" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH46" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ46">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="BK46">
+        <v>0</v>
+      </c>
+      <c r="BL46">
+        <v>0</v>
+      </c>
+      <c r="BM46">
+        <v>0.62804249999999995</v>
+      </c>
+      <c r="BN46">
+        <v>2.7999999999999997E-2</v>
+      </c>
+      <c r="BO46">
+        <v>0</v>
+      </c>
+      <c r="BP46">
+        <v>0</v>
+      </c>
+      <c r="BQ46">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="BR46" s="26"/>
+    </row>
+    <row r="47" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+      <c r="AB47" s="16"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
+      <c r="AF47" s="16"/>
+      <c r="AG47" s="16"/>
+      <c r="AH47" s="17"/>
+      <c r="AI47" s="17"/>
+      <c r="AJ47" s="17"/>
+      <c r="AK47" s="17"/>
+      <c r="AL47" s="17"/>
+      <c r="AM47" s="17"/>
+      <c r="AN47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR47" s="17">
+        <v>0.65</v>
+      </c>
+      <c r="AS47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AU47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AW47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AX47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY47" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BC47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI47" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ47">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="BK47">
+        <v>0</v>
+      </c>
+      <c r="BL47">
+        <v>0</v>
+      </c>
+      <c r="BM47">
+        <v>0</v>
+      </c>
+      <c r="BN47">
+        <v>0</v>
+      </c>
+      <c r="BO47">
+        <v>0</v>
+      </c>
+      <c r="BP47">
+        <v>0</v>
+      </c>
+      <c r="BQ47">
+        <v>0</v>
+      </c>
+      <c r="BR47" s="26"/>
+    </row>
+    <row r="48" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+      <c r="AB48" s="16"/>
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
+      <c r="AF48" s="16"/>
+      <c r="AG48" s="16"/>
+      <c r="AH48" s="17"/>
+      <c r="AI48" s="17"/>
+      <c r="AJ48" s="17"/>
+      <c r="AK48" s="17"/>
+      <c r="AL48" s="17"/>
+      <c r="AM48" s="17"/>
+      <c r="AN48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR48" s="17">
+        <v>0.88985592777174805</v>
+      </c>
+      <c r="AS48" s="17">
+        <v>1.8690214168039541E-2</v>
+      </c>
+      <c r="AT48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AU48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AW48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AX48" s="17">
+        <v>3.1493015972768802E-2</v>
+      </c>
+      <c r="AY48" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ48" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA48" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB48" s="17">
+        <v>0</v>
+      </c>
+      <c r="BC48" s="17">
+        <v>2.9667063435564096E-2</v>
+      </c>
+      <c r="BD48" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE48" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF48" s="17">
+        <v>3.0293778651879519E-2</v>
+      </c>
+      <c r="BG48" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH48" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ48">
+        <v>0</v>
+      </c>
+      <c r="BK48">
+        <v>0</v>
+      </c>
+      <c r="BL48">
+        <v>0</v>
+      </c>
+      <c r="BM48">
+        <v>0</v>
+      </c>
+      <c r="BN48">
+        <v>0</v>
+      </c>
+      <c r="BO48">
+        <v>0</v>
+      </c>
+      <c r="BP48">
+        <v>0</v>
+      </c>
+      <c r="BQ48">
+        <v>0</v>
+      </c>
+      <c r="BR48" s="26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="16"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="16"/>
+      <c r="W49" s="16"/>
+      <c r="X49" s="16"/>
+      <c r="Y49" s="16"/>
+      <c r="Z49" s="16"/>
+      <c r="AA49" s="16"/>
+      <c r="AB49" s="16"/>
+      <c r="AC49" s="16"/>
+      <c r="AD49" s="16"/>
+      <c r="AE49" s="16"/>
+      <c r="AF49" s="16"/>
+      <c r="AG49" s="16"/>
+      <c r="AH49" s="17"/>
+      <c r="AI49" s="17"/>
+      <c r="AJ49" s="17"/>
+      <c r="AK49" s="17"/>
+      <c r="AL49" s="17"/>
+      <c r="AM49" s="17"/>
+      <c r="AN49" s="17">
+        <v>0.17874000000000004</v>
+      </c>
+      <c r="AO49" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR49" s="17">
+        <v>0.71188474221739839</v>
+      </c>
+      <c r="AS49" s="17">
+        <v>1.4952171334431635E-2</v>
+      </c>
+      <c r="AT49" s="17">
+        <v>4.6000000000000007E-4</v>
+      </c>
+      <c r="AU49" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV49" s="17">
+        <v>3.2000000000000006E-3</v>
+      </c>
+      <c r="AW49" s="17">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AX49" s="17">
+        <v>2.5194412778215047E-2</v>
+      </c>
+      <c r="AY49" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ49" s="17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BA49" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB49" s="17">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="BC49" s="17">
+        <v>2.3733650748451275E-2</v>
+      </c>
+      <c r="BD49" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE49" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF49" s="17">
+        <v>2.4235022921503618E-2</v>
+      </c>
+      <c r="BG49" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH49" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI49" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ49">
+        <v>4.0000000000000007E-4</v>
+      </c>
+      <c r="BK49">
+        <v>0</v>
+      </c>
+      <c r="BL49">
+        <v>0</v>
+      </c>
+      <c r="BM49">
+        <v>2.0000000000000004E-4</v>
+      </c>
+      <c r="BN49">
+        <v>0</v>
+      </c>
+      <c r="BO49">
+        <v>0</v>
+      </c>
+      <c r="BP49">
+        <v>0</v>
+      </c>
+      <c r="BQ49">
+        <v>1.12E-2</v>
+      </c>
+      <c r="BR49" s="26"/>
+    </row>
+    <row r="50" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16"/>
+      <c r="S50" s="16"/>
+      <c r="T50" s="16"/>
+      <c r="U50" s="16"/>
+      <c r="V50" s="16"/>
+      <c r="W50" s="16"/>
+      <c r="X50" s="16"/>
+      <c r="Y50" s="16"/>
+      <c r="Z50" s="16"/>
+      <c r="AA50" s="16"/>
+      <c r="AB50" s="16"/>
+      <c r="AC50" s="16"/>
+      <c r="AD50" s="16"/>
+      <c r="AE50" s="16"/>
+      <c r="AF50" s="16"/>
+      <c r="AG50" s="16"/>
+      <c r="AH50" s="17"/>
+      <c r="AI50" s="17"/>
+      <c r="AJ50" s="17"/>
+      <c r="AK50" s="17"/>
+      <c r="AL50" s="17"/>
+      <c r="AM50" s="17"/>
+      <c r="AN50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="17">
+        <v>0.41071024702423337</v>
+      </c>
+      <c r="AP50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AU50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV50" s="17">
+        <v>0.24195261770755364</v>
+      </c>
+      <c r="AW50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AX50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY50" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BC50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI50" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ50">
+        <v>0</v>
+      </c>
+      <c r="BK50">
+        <v>0</v>
+      </c>
+      <c r="BL50">
+        <v>0</v>
+      </c>
+      <c r="BM50">
+        <v>0</v>
+      </c>
+      <c r="BN50">
+        <v>0</v>
+      </c>
+      <c r="BO50">
+        <v>0</v>
+      </c>
+      <c r="BP50">
+        <v>0.34733713526821314</v>
+      </c>
+      <c r="BQ50">
+        <v>0</v>
+      </c>
+      <c r="BR50" s="26"/>
+    </row>
+    <row r="51" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
+      <c r="R51" s="16"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
+      <c r="Z51" s="16"/>
+      <c r="AA51" s="16"/>
+      <c r="AB51" s="16"/>
+      <c r="AC51" s="16"/>
+      <c r="AD51" s="16"/>
+      <c r="AE51" s="16"/>
+      <c r="AF51" s="16"/>
+      <c r="AG51" s="16"/>
+      <c r="AH51" s="17"/>
+      <c r="AI51" s="17"/>
+      <c r="AJ51" s="17"/>
+      <c r="AK51" s="17"/>
+      <c r="AL51" s="17"/>
+      <c r="AM51" s="17"/>
+      <c r="AN51" s="17">
+        <v>8.5011764705882398E-2</v>
+      </c>
+      <c r="AO51" s="17">
+        <v>8.3250000000000002E-4</v>
+      </c>
+      <c r="AP51" s="17">
+        <v>8.3249999999999991E-4</v>
+      </c>
+      <c r="AQ51" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR51" s="17">
+        <v>8.8967451911966602E-2</v>
+      </c>
+      <c r="AS51" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT51" s="17">
+        <v>0</v>
+      </c>
+      <c r="AU51" s="17">
+        <v>2.2336133642363462E-2</v>
+      </c>
+      <c r="AV51" s="17">
+        <v>0.36624263044190586</v>
+      </c>
+      <c r="AW51" s="17">
+        <v>0.13905470588235291</v>
+      </c>
+      <c r="AX51" s="17">
+        <v>2.7407368488316783E-3</v>
+      </c>
+      <c r="AY51" s="17">
+        <v>8.7320502683172901E-3</v>
+      </c>
+      <c r="AZ51" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA51" s="17">
+        <v>4.8367431155282484E-2</v>
+      </c>
+      <c r="BB51" s="17">
+        <v>0</v>
+      </c>
+      <c r="BC51" s="17">
+        <v>2.5389881641260134E-3</v>
+      </c>
+      <c r="BD51" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE51" s="17">
+        <v>6.973839830689807E-2</v>
+      </c>
+      <c r="BF51" s="17">
+        <v>8.0511004522441337E-2</v>
+      </c>
+      <c r="BG51" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH51" s="17">
+        <v>4.9950000000000003E-3</v>
+      </c>
+      <c r="BI51" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ51">
+        <v>5.5280985463974468E-2</v>
+      </c>
+      <c r="BK51">
+        <v>4.3901605528137884E-3</v>
+      </c>
+      <c r="BL51">
+        <v>1.9427558132843741E-2</v>
+      </c>
+      <c r="BM51">
+        <v>0</v>
+      </c>
+      <c r="BN51">
+        <v>0</v>
+      </c>
+      <c r="BO51">
+        <v>0</v>
+      </c>
+      <c r="BP51">
+        <v>0</v>
+      </c>
+      <c r="BQ51">
+        <v>0</v>
+      </c>
+      <c r="BR51" s="26"/>
+    </row>
+    <row r="52" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="16"/>
+      <c r="V52" s="16"/>
+      <c r="W52" s="16"/>
+      <c r="X52" s="16"/>
+      <c r="Y52" s="16"/>
+      <c r="Z52" s="16"/>
+      <c r="AA52" s="16"/>
+      <c r="AB52" s="16"/>
+      <c r="AC52" s="16"/>
+      <c r="AD52" s="16"/>
+      <c r="AE52" s="16"/>
+      <c r="AF52" s="16"/>
+      <c r="AG52" s="16"/>
+      <c r="AH52" s="17"/>
+      <c r="AI52" s="17"/>
+      <c r="AJ52" s="17"/>
+      <c r="AK52" s="17"/>
+      <c r="AL52" s="17"/>
+      <c r="AM52" s="17"/>
+      <c r="AN52" s="17">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AO52" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="17">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="AR52" s="17">
+        <v>1E-3</v>
+      </c>
+      <c r="AS52" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="17">
+        <v>0.2175</v>
+      </c>
+      <c r="AU52" s="17">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AV52" s="17">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AW52" s="17">
+        <v>0.185</v>
+      </c>
+      <c r="AX52" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY52" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ52" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA52" s="17">
+        <v>0.09</v>
+      </c>
+      <c r="BB52" s="17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BC52" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD52" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE52" s="17">
+        <v>0.46936</v>
+      </c>
+      <c r="BF52" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG52" s="17">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="BH52" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="17">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="BJ52">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BK52">
+        <v>0</v>
+      </c>
+      <c r="BL52">
+        <v>0</v>
+      </c>
+      <c r="BM52">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="BN52">
+        <v>0</v>
+      </c>
+      <c r="BO52">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BP52">
+        <v>0</v>
+      </c>
+      <c r="BQ52">
+        <v>0</v>
+      </c>
+      <c r="BR52" s="26"/>
+    </row>
+    <row r="53" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
+      <c r="O53" s="16"/>
+      <c r="P53" s="16"/>
+      <c r="Q53" s="16"/>
+      <c r="R53" s="16"/>
+      <c r="S53" s="16"/>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16"/>
+      <c r="V53" s="16"/>
+      <c r="W53" s="16"/>
+      <c r="X53" s="16"/>
+      <c r="Y53" s="16"/>
+      <c r="Z53" s="16"/>
+      <c r="AA53" s="16"/>
+      <c r="AB53" s="16"/>
+      <c r="AC53" s="16"/>
+      <c r="AD53" s="16"/>
+      <c r="AE53" s="16"/>
+      <c r="AF53" s="16"/>
+      <c r="AG53" s="16"/>
+      <c r="AH53" s="17"/>
+      <c r="AI53" s="17"/>
+      <c r="AJ53" s="17"/>
+      <c r="AK53" s="17"/>
+      <c r="AL53" s="17"/>
+      <c r="AM53" s="17"/>
+      <c r="AN53" s="17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AO53" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="17">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="AR53" s="17">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="AS53" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT53" s="17">
+        <v>0.19</v>
+      </c>
+      <c r="AU53" s="17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AV53" s="17">
+        <v>1.5E-3</v>
+      </c>
+      <c r="AW53" s="17">
+        <v>0.17842000000000005</v>
+      </c>
+      <c r="AX53" s="17">
+        <v>0</v>
+      </c>
+      <c r="AY53" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA53" s="17">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="BB53" s="17">
+        <v>1.7499999999999998E-3</v>
+      </c>
+      <c r="BC53" s="17">
+        <v>0</v>
+      </c>
+      <c r="BD53" s="17">
+        <v>5.1250000000000004E-2</v>
+      </c>
+      <c r="BE53" s="17">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="BF53" s="17">
+        <v>0</v>
+      </c>
+      <c r="BG53" s="17">
+        <v>7.4999999999999993E-5</v>
+      </c>
+      <c r="BH53" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI53" s="17">
+        <v>7.4999999999999993E-5</v>
+      </c>
+      <c r="BJ53">
+        <v>1.7499999999999998E-3</v>
+      </c>
+      <c r="BK53">
+        <v>0</v>
+      </c>
+      <c r="BL53">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="BM53">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="BN53">
+        <v>0</v>
+      </c>
+      <c r="BO53">
+        <v>0</v>
+      </c>
+      <c r="BP53">
+        <v>0</v>
+      </c>
+      <c r="BQ53">
+        <v>0</v>
+      </c>
+      <c r="BR53" s="26" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="16"/>
+      <c r="Q54" s="16"/>
+      <c r="R54" s="16"/>
+      <c r="S54" s="16"/>
+      <c r="T54" s="16"/>
+      <c r="U54" s="16"/>
+      <c r="V54" s="16"/>
+      <c r="W54" s="16"/>
+      <c r="X54" s="16"/>
+      <c r="Y54" s="16"/>
+      <c r="Z54" s="16"/>
+      <c r="AA54" s="16"/>
+      <c r="AB54" s="16"/>
+      <c r="AC54" s="16"/>
+      <c r="AD54" s="16"/>
+      <c r="AE54" s="16"/>
+      <c r="AF54" s="16"/>
+      <c r="AG54" s="16"/>
+      <c r="AH54" s="17"/>
+      <c r="AI54" s="17"/>
+      <c r="AJ54" s="17"/>
+      <c r="AK54" s="17"/>
+      <c r="AL54" s="17"/>
+      <c r="AM54" s="17"/>
+      <c r="AN54" s="17">
+        <v>0.51847200000000004</v>
+      </c>
+      <c r="AO54" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP54" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ54" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR54" s="17">
+        <v>1.4100000000000001E-4</v>
+      </c>
+      <c r="AS54" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT54" s="17">
+        <v>2.5787999999999998E-2</v>
+      </c>
+      <c r="AU54" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV54" s="17">
+        <v>8.9600000000000009E-3</v>
+      </c>
+      <c r="AW54" s="17">
+        <v>9.5856499999999983E-2</v>
+      </c>
+      <c r="AX54" s="17">
+        <v>2.2499999999999998E-5</v>
+      </c>
+      <c r="AY54" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ54" s="17">
+        <v>1.3999999999999999E-2</v>
+      </c>
+      <c r="BA54" s="17">
+        <v>3.15E-3</v>
+      </c>
+      <c r="BB54" s="17">
+        <v>2.2399999999999998E-3</v>
+      </c>
+      <c r="BC54" s="17">
+        <v>1.45E-4</v>
+      </c>
+      <c r="BD54" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE54" s="17">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BF54" s="17">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="BG54" s="17">
+        <v>3.1499999999999993E-5</v>
+      </c>
+      <c r="BH54" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI54" s="17">
+        <v>2.0999999999999999E-5</v>
+      </c>
+      <c r="BJ54">
+        <v>1.82E-3</v>
+      </c>
+      <c r="BK54">
+        <v>0</v>
+      </c>
+      <c r="BL54">
+        <v>0</v>
+      </c>
+      <c r="BM54">
+        <v>0.26959249999999996</v>
+      </c>
+      <c r="BN54">
+        <v>1.2E-2</v>
+      </c>
+      <c r="BO54">
+        <v>0</v>
+      </c>
+      <c r="BP54">
+        <v>0</v>
+      </c>
+      <c r="BQ54">
+        <v>3.1359999999999999E-2</v>
+      </c>
+      <c r="BR54" s="26"/>
+    </row>
+    <row r="55" spans="1:70" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+      <c r="N55" s="16"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="16"/>
+      <c r="Q55" s="16"/>
+      <c r="R55" s="16"/>
+      <c r="S55" s="16"/>
+      <c r="T55" s="16"/>
+      <c r="U55" s="16"/>
+      <c r="V55" s="16"/>
+      <c r="W55" s="16"/>
+      <c r="X55" s="16"/>
+      <c r="Y55" s="16"/>
+      <c r="Z55" s="16"/>
+      <c r="AA55" s="16"/>
+      <c r="AB55" s="16"/>
+      <c r="AC55" s="16"/>
+      <c r="AD55" s="16"/>
+      <c r="AE55" s="16"/>
+      <c r="AF55" s="16"/>
+      <c r="AG55" s="16"/>
+      <c r="AH55" s="17"/>
+      <c r="AI55" s="17"/>
+      <c r="AJ55" s="17"/>
+      <c r="AK55" s="17"/>
+      <c r="AL55" s="17"/>
+      <c r="AM55" s="17"/>
+      <c r="AN55" s="17">
+        <v>0.06</v>
+      </c>
+      <c r="AO55" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP55" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ55" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR55" s="17">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="AS55" s="17">
+        <v>0</v>
+      </c>
+      <c r="AT55" s="17">
+        <v>0</v>
+      </c>
+      <c r="AU55" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV55" s="17">
+        <v>0</v>
+      </c>
+      <c r="AW55" s="17">
+        <v>1.5E-3</v>
+      </c>
+      <c r="AX55" s="17">
+        <v>7.4999999999999993E-5</v>
+      </c>
+      <c r="AY55" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ55" s="17">
+        <v>0</v>
+      </c>
+      <c r="BA55" s="17">
+        <v>0</v>
+      </c>
+      <c r="BB55" s="17">
+        <v>0</v>
+      </c>
+      <c r="BC55" s="17">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="BD55" s="17">
+        <v>0</v>
+      </c>
+      <c r="BE55" s="17">
+        <v>0</v>
+      </c>
+      <c r="BF55" s="17">
+        <v>1E-3</v>
+      </c>
+      <c r="BG55" s="17">
+        <v>0</v>
+      </c>
+      <c r="BH55" s="17">
+        <v>0</v>
+      </c>
+      <c r="BI55" s="17">
+        <v>0</v>
+      </c>
+      <c r="BJ55">
+        <v>0</v>
+      </c>
+      <c r="BK55">
+        <v>0</v>
+      </c>
+      <c r="BL55">
+        <v>0</v>
+      </c>
+      <c r="BM55">
+        <v>0.89677499999999999</v>
+      </c>
+      <c r="BN55">
+        <v>0.04</v>
+      </c>
+      <c r="BO55">
+        <v>0</v>
+      </c>
+      <c r="BP55">
+        <v>0</v>
+      </c>
+      <c r="BQ55">
+        <v>0</v>
+      </c>
+      <c r="BR55" s="26" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BJ47" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BJ47">
+      <sortCondition descending="1" ref="B1:B47"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2433,30 +7319,30 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="B1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -2466,7 +7352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -2480,7 +7366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
